--- a/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
+++ b/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; EGP&quot;"/>
     <numFmt numFmtId="166" formatCode="0.000&quot;x&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -177,11 +177,17 @@
     <font>
       <name val="Inter"/>
       <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <b val="1"/>
       <color rgb="00111827"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -213,6 +219,11 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -240,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -483,6 +494,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -492,7 +506,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -59180,7 +59194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -59217,7 +59231,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="83" t="inlineStr">
         <is>
-          <t>⚠ The starting numbers below are placeholders so the status columns work on day one — they are not industry truth. Replace them with this client's own trailing 90-day range by month three. A benchmark you didn't measure is a guess, and clients can smell a guess.</t>
+          <t>⚠ The starting numbers below are placeholders so the status columns work on day one — they are not industry truth. Replace them with this client's own trailing 90-day range by month three. A benchmark you didn't measure is a guess, and clients can smell a guess.   •   Once you have replaced them, type TUNED in cell B28 below so Health Check stops flagging this tab.</t>
         </is>
       </c>
     </row>
@@ -59762,6 +59776,23 @@
       <c r="A25" s="89" t="inlineStr">
         <is>
           <t>Lower is better (CPM, CPC, Frequency, Breakeven ROAS): the same ladder, mirrored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Benchmarks tuning status</t>
+        </is>
+      </c>
+      <c r="B28" s="90" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Type TUNED here once the thresholds above are this client's own 90-day numbers.</t>
         </is>
       </c>
     </row>
@@ -59851,7 +59882,7 @@
           <t>Zero here means your date cells and your data don't overlap. Start here.</t>
         </is>
       </c>
-      <c r="E6" s="90" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>There is no universal good CPM.</t>
         </is>
@@ -59900,7 +59931,7 @@
           <t>First date in the data</t>
         </is>
       </c>
-      <c r="B9" s="91">
+      <c r="B9" s="92">
         <f>IFERROR(MIN(Fundamentals!$A$2:$A$6000),0)</f>
         <v/>
       </c>
@@ -59916,7 +59947,7 @@
           <t>Last date in the data</t>
         </is>
       </c>
-      <c r="B10" s="91">
+      <c r="B10" s="92">
         <f>IFERROR(MAX(Fundamentals!$A$2:$A$6000),0)</f>
         <v/>
       </c>
@@ -59984,7 +60015,7 @@
           <t>Data exists for the selected period</t>
         </is>
       </c>
-      <c r="B17" s="92">
+      <c r="B17" s="93">
         <f>IF('KPI Calc'!$B$10&gt;0,"OK","FIX")</f>
         <v/>
       </c>
@@ -60000,7 +60031,7 @@
           <t>Clicks never exceed impressions</t>
         </is>
       </c>
-      <c r="B18" s="92">
+      <c r="B18" s="93">
         <f>IF('KPI Calc'!$B$12&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
         <v/>
       </c>
@@ -60016,7 +60047,7 @@
           <t>Purchases never exceed clicks</t>
         </is>
       </c>
-      <c r="B19" s="92">
+      <c r="B19" s="93">
         <f>IF('KPI Calc'!$B$16&gt;'KPI Calc'!$B$12,"FIX","OK")</f>
         <v/>
       </c>
@@ -60032,7 +60063,7 @@
           <t>Add to cart never exceeds clicks</t>
         </is>
       </c>
-      <c r="B20" s="92">
+      <c r="B20" s="93">
         <f>IF('KPI Calc'!$B$14&gt;'KPI Calc'!$B$12,"CHECK","OK")</f>
         <v/>
       </c>
@@ -60048,7 +60079,7 @@
           <t>Reach never exceeds impressions</t>
         </is>
       </c>
-      <c r="B21" s="92">
+      <c r="B21" s="93">
         <f>IF('KPI Calc'!$B$11&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
         <v/>
       </c>
@@ -60064,7 +60095,7 @@
           <t>Revenue is present</t>
         </is>
       </c>
-      <c r="B22" s="92">
+      <c r="B22" s="93">
         <f>IF('KPI Calc'!$B$17&lt;=0,"FIX","OK")</f>
         <v/>
       </c>
@@ -60080,7 +60111,7 @@
           <t>Ad spend reconciles to ad-level spend</t>
         </is>
       </c>
-      <c r="B23" s="92">
+      <c r="B23" s="93">
         <f>IF(ABS(SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$9)/MAX(1,'KPI Calc'!$B$9)&gt;0.05,"CHECK","OK")</f>
         <v/>
       </c>
@@ -60096,7 +60127,7 @@
           <t>Ad-level purchases reconcile</t>
         </is>
       </c>
-      <c r="B24" s="92">
+      <c r="B24" s="93">
         <f>IF(ABS(SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$16)/MAX(1,'KPI Calc'!$B$16)&gt;0.08,"CHECK","OK")</f>
         <v/>
       </c>
@@ -60112,7 +60143,7 @@
           <t>Business inputs are filled in</t>
         </is>
       </c>
-      <c r="B25" s="92">
+      <c r="B25" s="93">
         <f>IF(OR('KPI Calc'!$J$5&lt;=0,'KPI Calc'!$J$7&lt;=0),"FIX","OK")</f>
         <v/>
       </c>
@@ -60128,7 +60159,7 @@
           <t>Contribution margin is plausible</t>
         </is>
       </c>
-      <c r="B26" s="92">
+      <c r="B26" s="93">
         <f>IF(OR('KPI Calc'!$B$33&lt;=0,'KPI Calc'!$B$33&gt;=1),"CHECK","OK")</f>
         <v/>
       </c>
@@ -60144,7 +60175,7 @@
           <t>No blank platforms in Fundamentals</t>
         </is>
       </c>
-      <c r="B27" s="92">
+      <c r="B27" s="93">
         <f>IF(SUMPRODUCT((Fundamentals!$A$2:$A$6000&lt;&gt;"")*(Fundamentals!$B$2:$B$6000=""))&gt;0,"CHECK","OK")</f>
         <v/>
       </c>
@@ -60160,18 +60191,18 @@
           <t>Benchmarks retuned for this account</t>
         </is>
       </c>
-      <c r="B28" s="92">
-        <f>IF(Benchmarks!$D$16=0,"CHECK","OK")</f>
+      <c r="B28" s="93">
+        <f>IF(Benchmarks!$B$28="TUNED","OK","CHECK")</f>
         <v/>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>Until you replace the placeholder thresholds, every Status column is a guess.</t>
+          <t>The Benchmarks tab still holds the shipped placeholders. Replace them with this client's own range, then set Benchmarks!B28 to TUNED.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="93">
+      <c r="A30" s="94">
         <f>IF(COUNTIF(B17:B28,"FIX")&gt;0,"⛔ "&amp;COUNTIF(B17:B28,"FIX")&amp;" check(s) need fixing before you report these numbers.",IF(COUNTIF(B17:B28,"CHECK")&gt;0,"⚠ "&amp;COUNTIF(B17:B28,"CHECK")&amp;" thing(s) to verify. They are usually benign — but verify them.","✅ All "&amp;COUNTA(B17:B28)&amp;" checks passed. This data is safe to report."))</f>
         <v/>
       </c>

--- a/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
+++ b/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
@@ -58047,7 +58047,7 @@
         <v/>
       </c>
       <c r="F22" s="69">
-        <f>REPT("█",ROUND(20*IFERROR(C22,0),0))</f>
+        <f>REPT("█",ROUND(20*IFERROR(MIN(1,C22/D22),0),0))</f>
         <v/>
       </c>
     </row>
@@ -58074,7 +58074,7 @@
         <v/>
       </c>
       <c r="F23" s="69">
-        <f>REPT("█",ROUND(20*IFERROR(C23,0),0))</f>
+        <f>REPT("█",ROUND(20*IFERROR(MIN(1,C23/D23),0),0))</f>
         <v/>
       </c>
     </row>
@@ -58101,7 +58101,7 @@
         <v/>
       </c>
       <c r="F24" s="69">
-        <f>REPT("█",ROUND(20*IFERROR(C24,0),0))</f>
+        <f>REPT("█",ROUND(20*IFERROR(MIN(1,C24/D24),0),0))</f>
         <v/>
       </c>
     </row>
@@ -58128,7 +58128,7 @@
         <v/>
       </c>
       <c r="F25" s="69">
-        <f>REPT("█",ROUND(20*IFERROR(C25,0),0))</f>
+        <f>REPT("█",ROUND(20*IFERROR(MIN(1,C25/D25),0),0))</f>
         <v/>
       </c>
     </row>
@@ -58143,7 +58143,7 @@
         <v/>
       </c>
       <c r="C26" s="78">
-        <f>'KPI Calc'!B27</f>
+        <f>IF(B26=0,"—",'KPI Calc'!B27)</f>
         <v/>
       </c>
       <c r="D26" s="76">
@@ -58155,7 +58155,7 @@
         <v/>
       </c>
       <c r="F26" s="69">
-        <f>REPT("█",ROUND(20*IFERROR(C26,0),0))</f>
+        <f>REPT("█",ROUND(20*IFERROR(MIN(1,C26/D26),0),0))</f>
         <v/>
       </c>
       <c r="G26" s="79" t="inlineStr">
@@ -58193,7 +58193,7 @@
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="80">
-        <f>"Movement: spend "&amp;IF('KPI Calc'!E9&gt;=0,"up","down")&amp;" "&amp;TEXT(ABS('KPI Calc'!E9),"0%")&amp;" while revenue "&amp;IF('KPI Calc'!E17&gt;=0,"rose","fell")&amp;" "&amp;TEXT(ABS('KPI Calc'!E17),"0%")&amp;", so ROAS "&amp;IF('KPI Calc'!B30&gt;='KPI Calc'!C30,"improved","slipped")&amp;" from "&amp;ROUND('KPI Calc'!C30,2)&amp;"x to "&amp;ROUND('KPI Calc'!B30,2)&amp;"x. Costs per thousand impressions went from "&amp;TEXT(ROUND('KPI Calc'!C19,0),"#,##0")&amp;" to "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;".",</f>
+        <f>"Movement: spend "&amp;IF('KPI Calc'!E9&gt;=0,"up","down")&amp;" "&amp;TEXT(ABS('KPI Calc'!E9),"0%")&amp;" while revenue "&amp;IF('KPI Calc'!E17&gt;=0,"rose","fell")&amp;" "&amp;TEXT(ABS('KPI Calc'!E17),"0%")&amp;", so ROAS "&amp;IF('KPI Calc'!B30&gt;='KPI Calc'!C30,"improved","slipped")&amp;" from "&amp;ROUND('KPI Calc'!C30,2)&amp;"x to "&amp;ROUND('KPI Calc'!B30,2)&amp;"x. Costs per thousand impressions went from "&amp;TEXT(ROUND('KPI Calc'!C19,0),"#,##0")&amp;" to "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;"."</f>
         <v/>
       </c>
       <c r="B30" s="54" t="n"/>
@@ -58219,7 +58219,7 @@
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="80">
-        <f>"Efficiency read: CPM "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;", CTR "&amp;TEXT('KPI Calc'!B21,"0.00%")&amp;", click-to-purchase "&amp;TEXT('KPI Calc'!B26,"0.00%")&amp;", AOV "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". Frequency is "&amp;ROUND('KPI Calc'!B22,2)&amp;", "&amp;IF('KPI Calc'!B22&gt;3.5,"which is high enough that creative fatigue is now a budget risk — fresh assets before we scale.","which leaves room to add budget without hitting fatigue.")</f>
+        <f>"Efficiency read: CPM "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;", CTR "&amp;TEXT('KPI Calc'!B21,"0.00%")&amp;", click-to-purchase "&amp;TEXT('KPI Calc'!B26,"0.00%")&amp;", AOV "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". Frequency is "&amp;ROUND('KPI Calc'!B22,2)&amp;", "&amp;IF('KPI Calc'!B22&gt;3.5,"which is high enough that creative fatigue is now a budget risk — fresh assets before we scale.",IF('KPI Calc'!B26&lt;'KPI Calc'!C26*0.85,"which is below the fatigue line, so this is a conversion problem rather than a fatigue one: click-to-purchase fell from "&amp;TEXT('KPI Calc'!C26,"0.00%")&amp;" to "&amp;TEXT('KPI Calc'!B26,"0.00%")&amp;". Fix traffic quality and the landing page before adding budget.","which leaves room to add budget without hitting fatigue."))</f>
         <v/>
       </c>
       <c r="B32" s="54" t="n"/>
@@ -58232,7 +58232,7 @@
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="80">
-        <f>"Cost per purchase is "&amp;TEXT(ROUND('KPI Calc'!B28,0),"#,##0")&amp;" against an AOV of "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". At a "&amp;TEXT('KPI Calc'!B33,"0.0%")&amp;" contribution margin, breakeven ROAS is "&amp;ROUND('KPI Calc'!B35,2)&amp;"x, and headroom before we hit it is roughly "&amp;TEXT(ROUND(MAX(0,'KPI Calc'!B17*'KPI Calc'!B33-'KPI Calc'!B9),0),"#,##0")&amp;" more in spend at today's efficiency.",</f>
+        <f>"Cost per purchase is "&amp;TEXT(ROUND('KPI Calc'!B28,0),"#,##0")&amp;" against an AOV of "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". At a "&amp;TEXT('KPI Calc'!B33,"0.0%")&amp;" contribution margin, breakeven ROAS is "&amp;ROUND('KPI Calc'!B35,2)&amp;"x, and headroom before we hit it is roughly "&amp;TEXT(ROUND(MAX(0,'KPI Calc'!B17*'KPI Calc'!B33-'KPI Calc'!B9),0),"#,##0")&amp;" more in spend at today's efficiency."</f>
         <v/>
       </c>
       <c r="B33" s="54" t="n"/>
@@ -59827,7 +59827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -60140,86 +60140,102 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
+          <t>Checkout does not exceed add to cart</t>
+        </is>
+      </c>
+      <c r="B25" s="93">
+        <f>IF('KPI Calc'!$B$15&gt;'KPI Calc'!$B$14,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Initiate-checkout above add-to-cart breaks the funnel ladder. Usually a buy-now button that skips the cart, or events that are counted on the wrong step — confirm which before you quote the funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
           <t>Business inputs are filled in</t>
         </is>
       </c>
-      <c r="B25" s="93">
+      <c r="B26" s="93">
         <f>IF(OR('KPI Calc'!$J$5&lt;=0,'KPI Calc'!$J$7&lt;=0),"FIX","OK")</f>
         <v/>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>COGS % and shipping per order drive every profit number in the kit.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Contribution margin is plausible</t>
         </is>
       </c>
-      <c r="B26" s="93">
+      <c r="B27" s="93">
         <f>IF(OR('KPI Calc'!$B$33&lt;=0,'KPI Calc'!$B$33&gt;=1),"CHECK","OK")</f>
         <v/>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>A margin outside 0–100% means a cost input is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>No blank platforms in Fundamentals</t>
         </is>
       </c>
-      <c r="B27" s="93">
+      <c r="B28" s="93">
         <f>IF(SUMPRODUCT((Fundamentals!$A$2:$A$6000&lt;&gt;"")*(Fundamentals!$B$2:$B$6000=""))&gt;0,"CHECK","OK")</f>
         <v/>
       </c>
-      <c r="C27" s="37" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>Counts only rows that carry a date -- the empty rows below your data are normal and are ignored.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Benchmarks retuned for this account</t>
         </is>
       </c>
-      <c r="B28" s="93">
+      <c r="B29" s="93">
         <f>IF(Benchmarks!$B$28="TUNED","OK","CHECK")</f>
         <v/>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>The Benchmarks tab still holds the shipped placeholders. Replace them with this client's own range, then set Benchmarks!B28 to TUNED.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="94">
-        <f>IF(COUNTIF(B17:B28,"FIX")&gt;0,"⛔ "&amp;COUNTIF(B17:B28,"FIX")&amp;" check(s) need fixing before you report these numbers.",IF(COUNTIF(B17:B28,"CHECK")&gt;0,"⚠ "&amp;COUNTIF(B17:B28,"CHECK")&amp;" thing(s) to verify. They are usually benign — but verify them.","✅ All "&amp;COUNTA(B17:B28)&amp;" checks passed. This data is safe to report."))</f>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="94">
+        <f>IF(COUNTIF(B17:B29,"FIX")&gt;0,"⛔ "&amp;COUNTIF(B17:B29,"FIX")&amp;" check(s) need fixing before you report these numbers.",IF(COUNTIF(B17:B29,"CHECK")&gt;0,"⚠ "&amp;COUNTIF(B17:B29,"CHECK")&amp;" thing(s) to verify. They are usually benign — but verify them.","✅ All "&amp;COUNTA(B17:B29)&amp;" checks passed. This data is safe to report."))</f>
         <v/>
       </c>
-      <c r="B30" s="58" t="n"/>
-      <c r="C30" s="58" t="n"/>
+      <c r="B31" s="58" t="n"/>
+      <c r="C31" s="58" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E7:F20"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A30:C30"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
-  <conditionalFormatting sqref="B17:B28">
+  <conditionalFormatting sqref="B17:B29">
     <cfRule type="expression" priority="1" dxfId="6">
       <formula>B17="FIX"</formula>
     </cfRule>

--- a/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
+++ b/Client Reporting Kit/01_Google_Sheets_Reporting_Dashboard.xlsx
@@ -11,14 +11,18 @@
     <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Ad Data" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="KPI Calc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Ad Performance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Benchmarks" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Health Check" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="_Control" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Meta Dashboard" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TikTok Dashboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ad Performance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Health Check" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fundamentals'!$A$1:$K$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ad Data'!$A$1:$K$1081</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ad Performance'!$A$5:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,12 +30,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; EGP&quot;"/>
     <numFmt numFmtId="166" formatCode="0.000&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +176,12 @@
     </font>
     <font>
       <name val="Inter"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Inter"/>
       <b val="1"/>
       <color rgb="00B91C1C"/>
       <sz val="9"/>
@@ -187,7 +199,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -207,6 +219,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -251,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -314,7 +331,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -326,10 +343,10 @@
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -395,10 +412,26 @@
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -406,7 +439,6 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -419,19 +451,16 @@
     <xf numFmtId="3" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -468,19 +497,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -489,31 +512,40 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
     <dxf>
       <font>
         <name val="Inter"/>
@@ -570,15 +602,43 @@
     <dxf>
       <font>
         <name val="Inter"/>
-        <b val="1"/>
-        <color rgb="001D4ED8"/>
+        <color rgb="0015803D"/>
         <sz val="9"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DBEAFE"/>
+          <fgColor rgb="00DCFCE7"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Inter"/>
+        <i val="1"/>
+        <color rgb="006B7280"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Inter"/>
+        <b val="1"/>
+        <color rgb="0015803D"/>
+        <sz val="10"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Inter"/>
+        <b val="1"/>
+        <color rgb="00B91C1C"/>
+        <sz val="10"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -981,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1131,7 @@
     <row r="12" ht="28" customHeight="1">
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Open KPI Calc. In row 4 put the period you're reporting. In row 5 put what you're comparing it to. Everything else moves.</t>
+          <t>Open _Control and set the four dates — current period and what you compare it against. Everything else in the kit moves with them. If the n8n refresh workflow is running, it writes these for you.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1330,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="42.97499999999999" customHeight="1">
+    <row r="32" ht="55.3" customHeight="1">
       <c r="B32" s="11" t="inlineStr">
         <is>
           <t>LPV formula</t>
@@ -1279,18 +1339,31 @@
       <c r="C32" s="12" t="inlineStr">
         <is>
           <t>=ARRAYFORMULA(IF($A$2:$A="","",
-  SUMIF(IMPORTRANGE($N$1,"'Daily_Raw_Meta_Ads'!A$2:A"),$A$2:$A,
+  SUMIF(IMPORTRANGE($N$1,"'Daily_Raw_Meta_Ads'!A$2:A"),
+        TEXT($A$2:$A,"yyyy-mm-dd"),
         IMPORTRANGE($N$1,"'Daily_Raw_Meta_Ads'!N$2:N"))))</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="44" customHeight="1">
+    <row r="33" ht="58.2" customHeight="1">
       <c r="B33" s="11" t="inlineStr">
         <is>
+          <t>Why TEXT() is in there</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Daily_Raw_Meta_Ads stores its dates as TEXT ("2026-10-01"), while column A of this tab holds real dates. SUMIF will not match a real date against text, so it silently returns 0 and the click-to-landing-page rate reads 0.0% — which looks like a page-speed disaster rather than a formula that never matched. TEXT() turns the criteria into the same string the raw tab holds. If you ever normalise that column to real dates, remove the TEXT() wrapper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="71.25" customHeight="1">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>If the numbers look wrong</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Two things cause almost every problem. (1) Column A must be a real date, not text — select it and check Format ▸ Number ▸ Date shows something sensible. If it is text, the date filters silently return zero. (2) You must approve the IMPORTRANGE access prompt — the first paste shows a #REF! and a button, and it only works after you click Allow. Run Health Check afterwards: it reports the row count and first/last date, which tells you immediately whether the link worked.</t>
         </is>
@@ -1302,6 +1375,1066 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B10:C10"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>These thresholds decide every Status column in the kit. Retune them per account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>All amounts in EGP. Change the currency label on 'Start Here' after you copy this file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="92" t="inlineStr">
+        <is>
+          <t>⚠ The starting numbers below are placeholders so the status columns work on day one — they are not industry truth. Replace them with this client's own trailing 90-day range by month three. A benchmark you didn't measure is a guess, and clients can smell a guess.   •   Once you have replaced them, type TUNED in cell B28 below so Health Check stops flagging this tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6">
+      <c r="A6" s="68" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>Your value</t>
+        </is>
+      </c>
+      <c r="C6" s="69" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="D6" s="69" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="E6" s="69" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F6" s="69" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="G6" s="69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H6" s="68" t="inlineStr">
+        <is>
+          <t>If it's below target, look here first</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="B7" s="70">
+        <f>'KPI Calc'!B19</f>
+        <v/>
+      </c>
+      <c r="C7" s="85" t="n">
+        <v>140</v>
+      </c>
+      <c r="D7" s="85" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" s="85" t="n">
+        <v>72</v>
+      </c>
+      <c r="F7" s="85" t="n">
+        <v>55</v>
+      </c>
+      <c r="G7" s="36">
+        <f>IF($B7=0,"—",IF($B7&lt;=F7,"Strong",IF($B7&lt;=E7,"Target",IF($B7&lt;=D7,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="37" t="inlineStr">
+        <is>
+          <t>Auction pressure, audience saturation, or broad targeting diluting the mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="B8" s="70">
+        <f>'KPI Calc'!B20</f>
+        <v/>
+      </c>
+      <c r="C8" s="85" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="85" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E8" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="85" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="36">
+        <f>IF($B8=0,"—",IF($B8&lt;=F8,"Strong",IF($B8&lt;=E8,"Target",IF($B8&lt;=D8,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="37" t="inlineStr">
+        <is>
+          <t>Mostly CPM plus CTR. If CPC is high but CTR is fine, look at placement and audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B9" s="72">
+        <f>'KPI Calc'!B21</f>
+        <v/>
+      </c>
+      <c r="C9" s="80" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D9" s="80" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E9" s="80" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F9" s="80" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G9" s="36">
+        <f>IF($B9=0,"—",IF($B9&gt;=F9,"Strong",IF($B9&gt;=E9,"Target",IF($B9&gt;=D9,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="37" t="inlineStr">
+        <is>
+          <t>The creative hook — first 3 seconds of video, first line of primary text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Meta click to landing page</t>
+        </is>
+      </c>
+      <c r="B10" s="72">
+        <f>'KPI Calc'!B27</f>
+        <v/>
+      </c>
+      <c r="C10" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D10" s="80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="80" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F10" s="80" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G10" s="36">
+        <f>IF($B10=0,"—",IF($B10&gt;=F10,"Strong",IF($B10&gt;=E10,"Target",IF($B10&gt;=D10,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="37" t="inlineStr">
+        <is>
+          <t>Page speed and mobile load. A technical problem wearing a media costume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Click to add to cart</t>
+        </is>
+      </c>
+      <c r="B11" s="72">
+        <f>'KPI Calc'!B23</f>
+        <v/>
+      </c>
+      <c r="C11" s="80" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D11" s="80" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E11" s="80" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F11" s="80" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G11" s="36">
+        <f>IF($B11=0,"—",IF($B11&gt;=F11,"Strong",IF($B11&gt;=E11,"Target",IF($B11&gt;=D11,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="37" t="inlineStr">
+        <is>
+          <t>Product page: price positioning, imagery, reviews, delivery promise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Add to cart to checkout</t>
+        </is>
+      </c>
+      <c r="B12" s="72">
+        <f>'KPI Calc'!B24</f>
+        <v/>
+      </c>
+      <c r="C12" s="80" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D12" s="80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F12" s="80" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G12" s="36">
+        <f>IF($B12=0,"—",IF($B12&gt;=F12,"Strong",IF($B12&gt;=E12,"Target",IF($B12&gt;=D12,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>Shipping cost, surprise fees, forced account creation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Checkout to purchase</t>
+        </is>
+      </c>
+      <c r="B13" s="72">
+        <f>'KPI Calc'!B25</f>
+        <v/>
+      </c>
+      <c r="C13" s="80" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D13" s="80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="80" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F13" s="80" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G13" s="36">
+        <f>IF($B13=0,"—",IF($B13&gt;=F13,"Strong",IF($B13&gt;=E13,"Target",IF($B13&gt;=D13,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>Payment methods, cash on delivery, trust badges, retargeting coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Click to purchase CVR</t>
+        </is>
+      </c>
+      <c r="B14" s="72">
+        <f>'KPI Calc'!B26</f>
+        <v/>
+      </c>
+      <c r="C14" s="80" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D14" s="80" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E14" s="80" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F14" s="80" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G14" s="36">
+        <f>IF($B14=0,"—",IF($B14&gt;=F14,"Strong",IF($B14&gt;=E14,"Target",IF($B14&gt;=D14,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="37" t="inlineStr">
+        <is>
+          <t>End-to-end site conversion on paid clicks. Compare to this account's own history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B15" s="87">
+        <f>'KPI Calc'!B22</f>
+        <v/>
+      </c>
+      <c r="C15" s="88" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="88" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F15" s="88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" s="36">
+        <f>IF($B15=0,"—",IF($B15&lt;=F15,"Strong",IF($B15&lt;=E15,"Target",IF($B15&lt;=D15,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="37" t="inlineStr">
+        <is>
+          <t>Creative fatigue. Above target, refresh assets before adding budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="B16" s="70">
+        <f>'KPI Calc'!B29</f>
+        <v/>
+      </c>
+      <c r="C16" s="85" t="n">
+        <v>450</v>
+      </c>
+      <c r="D16" s="85" t="n">
+        <v>550</v>
+      </c>
+      <c r="E16" s="85" t="n">
+        <v>650</v>
+      </c>
+      <c r="F16" s="85" t="n">
+        <v>800</v>
+      </c>
+      <c r="G16" s="36">
+        <f>IF($B16=0,"—",IF($B16&gt;=F16,"Strong",IF($B16&gt;=E16,"Target",IF($B16&gt;=D16,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="37" t="inlineStr">
+        <is>
+          <t>Placeholder ladder — replace with this account's own trailing range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Revenue per 1,000 impressions</t>
+        </is>
+      </c>
+      <c r="B17" s="70">
+        <f>'KPI Calc'!B31</f>
+        <v/>
+      </c>
+      <c r="C17" s="85" t="n">
+        <v>80</v>
+      </c>
+      <c r="D17" s="85" t="n">
+        <v>120</v>
+      </c>
+      <c r="E17" s="85" t="n">
+        <v>170</v>
+      </c>
+      <c r="F17" s="85" t="n">
+        <v>250</v>
+      </c>
+      <c r="G17" s="36">
+        <f>IF($B17=0,"—",IF($B17&gt;=F17,"Strong",IF($B17&gt;=E17,"Target",IF($B17&gt;=D17,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="37" t="inlineStr">
+        <is>
+          <t>The cleanest single measure of end-to-end media efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="B18" s="71">
+        <f>'KPI Calc'!B30</f>
+        <v/>
+      </c>
+      <c r="C18" s="93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D18" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="93" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F18" s="93" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="36">
+        <f>IF($B18=0,"—",IF($B18&gt;=F18,"Strong",IF($B18&gt;=E18,"Target",IF($B18&gt;=D18,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>Never set a target below breakeven ROAS. Weak here sits below breakeven on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Breakeven ROAS</t>
+        </is>
+      </c>
+      <c r="B19" s="71">
+        <f>'KPI Calc'!B35</f>
+        <v/>
+      </c>
+      <c r="C19" s="93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="93" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="93" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="93" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G19" s="36">
+        <f>IF($B19=0,"—",IF($B19&lt;=F19,"Strong",IF($B19&lt;=E19,"Target",IF($B19&lt;=D19,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>Calculated from the client's own margin inputs. Do not overwrite this row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>POAS (profit on ad spend)</t>
+        </is>
+      </c>
+      <c r="B20" s="71">
+        <f>'KPI Calc'!B37</f>
+        <v/>
+      </c>
+      <c r="C20" s="93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="93" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E20" s="93" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F20" s="93" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G20" s="36">
+        <f>IF($B20=0,"—",IF($B20&gt;=F20,"Strong",IF($B20&gt;=E20,"Target",IF($B20&gt;=D20,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="37" t="inlineStr">
+        <is>
+          <t>Profit per unit of spend. The number to move once ROAS is acceptable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Contribution margin %</t>
+        </is>
+      </c>
+      <c r="B21" s="72">
+        <f>'KPI Calc'!B33</f>
+        <v/>
+      </c>
+      <c r="C21" s="80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D21" s="80" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E21" s="80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F21" s="80" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G21" s="36">
+        <f>IF($B21=0,"—",IF($B21&gt;=F21,"Strong",IF($B21&gt;=E21,"Target",IF($B21&gt;=D21,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="37" t="inlineStr">
+        <is>
+          <t>Driven by the client's cost inputs on KPI Calc, cells J5:J7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>How status is decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>Higher is better (CTR, rates, AOV, ROAS, POAS): Strong ≥ F, Target ≥ E, Watch ≥ D, otherwise Weak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>Lower is better (CPM, CPC, Frequency, Breakeven ROAS): the same ladder, mirrored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Benchmarks tuning status</t>
+        </is>
+      </c>
+      <c r="B28" s="96" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Type TUNED here once the thresholds above are this client's own 90-day numbers.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:H5"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G7:G21">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>$G7="Strong"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>$G7="Target"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="4">
+      <formula>$G7="Watch"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>$G7="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Health Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Run this before anything goes to a client. Data errors look exactly like performance problems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DATA COVERAGE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT COUNTS AS 'GOOD'</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Rows in the current period</t>
+        </is>
+      </c>
+      <c r="B6" s="58">
+        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
+        <v/>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Zero here means your date cells and your data don't overlap. Start here.</t>
+        </is>
+      </c>
+      <c r="E6" s="97" t="inlineStr">
+        <is>
+          <t>There is no universal good CPM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Distinct days present</t>
+        </is>
+      </c>
+      <c r="B7" s="58">
+        <f>SUMPRODUCT((COUNTIFS(Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)&gt;0)/COUNTIF(Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000&amp;""))</f>
+        <v/>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Should roughly equal the days in your period, per platform.</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>A CPM of 180 EGP is excellent for one category and fatal for another. The status column in this file compares this account against thresholds you control — start with the placeholders, then replace them with this client's own 90-day trailing range. That is the only benchmark that survives a client asking "compared to what?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Days in the period (calendar)</t>
+        </is>
+      </c>
+      <c r="B8" s="58">
+        <f>'KPI Calc'!$C$4-'KPI Calc'!$B$4+1</f>
+        <v/>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Compare with the row above. A big gap means missing sync days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>First date in the data</t>
+        </is>
+      </c>
+      <c r="B9" s="55">
+        <f>IFERROR(MIN(Fundamentals!$A$2:$A$6000),0)</f>
+        <v/>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Sanity-check the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Last date in the data</t>
+        </is>
+      </c>
+      <c r="B10" s="55">
+        <f>IFERROR(MAX(Fundamentals!$A$2:$A$6000),0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Should be yesterday or today if the pipeline is healthy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Meta rows in period</t>
+        </is>
+      </c>
+      <c r="B11" s="58">
+        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>TikTok rows in period</t>
+        </is>
+      </c>
+      <c r="B12" s="58">
+        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHECKS  —  red means fix the DATA, not the campaign</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>Data exists for the selected period</t>
+        </is>
+      </c>
+      <c r="B17" s="98">
+        <f>IF('KPI Calc'!$B$10&gt;0,"OK","FIX")</f>
+        <v/>
+      </c>
+      <c r="C17" s="37" t="inlineStr">
+        <is>
+          <t>No impressions in the period means the date cells are wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Clicks never exceed impressions</t>
+        </is>
+      </c>
+      <c r="B18" s="98">
+        <f>IF('KPI Calc'!$B$12&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
+        <v/>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>A clicks &gt; impressions read almost always means the wrong click column was pulled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Purchases never exceed clicks</t>
+        </is>
+      </c>
+      <c r="B19" s="98">
+        <f>IF('KPI Calc'!$B$16&gt;'KPI Calc'!$B$12,"FIX","OK")</f>
+        <v/>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>Either a view-through-heavy attribution window or mismatched date ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Add to cart never exceeds clicks</t>
+        </is>
+      </c>
+      <c r="B20" s="98">
+        <f>IF('KPI Calc'!$B$14&gt;'KPI Calc'!$B$12,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C20" s="37" t="inlineStr">
+        <is>
+          <t>Cross-platform ATC can exceed clicks if windows differ between platforms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Reach never exceeds impressions</t>
+        </is>
+      </c>
+      <c r="B21" s="98">
+        <f>IF('KPI Calc'!$B$11&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
+        <v/>
+      </c>
+      <c r="C21" s="37" t="inlineStr">
+        <is>
+          <t>Reach is deduplicated, so this is a hard rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Revenue is present</t>
+        </is>
+      </c>
+      <c r="B22" s="98">
+        <f>IF('KPI Calc'!$B$17&lt;=0,"FIX","OK")</f>
+        <v/>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>Without purchase value there is no ROAS, no AOV and no story to tell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>Ad spend reconciles to ad-level spend</t>
+        </is>
+      </c>
+      <c r="B23" s="98">
+        <f>IF(ABS(SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$9)/MAX(1,'KPI Calc'!$B$9)&gt;0.05,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C23" s="37" t="inlineStr">
+        <is>
+          <t>Sums ad-level spend for the SAME dates as the period, then compares it with account-level spend. More than 5% apart means the ad-level export is incomplete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>Ad-level purchases reconcile</t>
+        </is>
+      </c>
+      <c r="B24" s="98">
+        <f>IF(ABS(SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$16)/MAX(1,'KPI Calc'!$B$16)&gt;0.08,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Ad-level and account-level purchase counts should be close over the same dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>Checkout does not exceed add to cart</t>
+        </is>
+      </c>
+      <c r="B25" s="98">
+        <f>IF('KPI Calc'!$B$15&gt;'KPI Calc'!$B$14,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C25" s="37" t="inlineStr">
+        <is>
+          <t>Initiate-checkout above add-to-cart breaks the funnel ladder. Usually a buy-now button that skips the cart, or events that are counted on the wrong step — confirm which before you quote the funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>Business inputs are filled in</t>
+        </is>
+      </c>
+      <c r="B26" s="98">
+        <f>IF(OR('KPI Calc'!$J$5&lt;=0,'KPI Calc'!$J$7&lt;=0),"FIX","OK")</f>
+        <v/>
+      </c>
+      <c r="C26" s="37" t="inlineStr">
+        <is>
+          <t>COGS % and shipping per order drive every profit number in the kit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>Contribution margin is plausible</t>
+        </is>
+      </c>
+      <c r="B27" s="98">
+        <f>IF(OR('KPI Calc'!$B$33&lt;=0,'KPI Calc'!$B$33&gt;=1),"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C27" s="37" t="inlineStr">
+        <is>
+          <t>A margin outside 0–100% means a cost input is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>No blank platforms in Fundamentals</t>
+        </is>
+      </c>
+      <c r="B28" s="98">
+        <f>IF(SUMPRODUCT((Fundamentals!$A$2:$A$6000&lt;&gt;"")*(Fundamentals!$B$2:$B$6000=""))&gt;0,"CHECK","OK")</f>
+        <v/>
+      </c>
+      <c r="C28" s="37" t="inlineStr">
+        <is>
+          <t>Counts only rows that carry a date -- the empty rows below your data are normal and are ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>Benchmarks retuned for this account</t>
+        </is>
+      </c>
+      <c r="B29" s="98">
+        <f>IF(Benchmarks!$B$28="TUNED","OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>The Benchmarks tab still holds the shipped placeholders. Replace them with this client's own range, then set Benchmarks!B28 to TUNED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="99">
+        <f>IF(COUNTIF(B17:B29,"FIX")&gt;0,"⛔ "&amp;COUNTIF(B17:B29,"FIX")&amp;" check(s) need fixing before you report these numbers.",IF(COUNTIF(B17:B29,"CHECK")&gt;0,"⚠ "&amp;COUNTIF(B17:B29,"CHECK")&amp;" thing(s) to verify. They are usually benign — but verify them.","✅ All "&amp;COUNTA(B17:B29)&amp;" checks passed. This data is safe to report."))</f>
+        <v/>
+      </c>
+      <c r="B31" s="60" t="n"/>
+      <c r="C31" s="60" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="E7:F20"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B17:B29">
+    <cfRule type="expression" priority="1" dxfId="9">
+      <formula>B17="FIX"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="10">
+      <formula>B17="CHECK"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="11">
+      <formula>B17="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -56620,11 +57753,13 @@
           <t>Current period</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n">
-        <v>46266</v>
-      </c>
-      <c r="C4" s="26" t="n">
-        <v>46295</v>
+      <c r="B4" s="26">
+        <f>IF(ISNUMBER(_Control!$B$2),_Control!$B$2,IFERROR(DATE(VALUE(MID(_Control!$B$2,1,4)),VALUE(MID(_Control!$B$2,6,2)),VALUE(MID(_Control!$B$2,9,2))),_Control!$B$2))</f>
+        <v/>
+      </c>
+      <c r="C4" s="26">
+        <f>IF(ISNUMBER(_Control!$B$3),_Control!$B$3,IFERROR(DATE(VALUE(MID(_Control!$B$3,1,4)),VALUE(MID(_Control!$B$3,6,2)),VALUE(MID(_Control!$B$3,9,2))),_Control!$B$3))</f>
+        <v/>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
@@ -56638,11 +57773,13 @@
           <t>Compare against</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
-        <v>46235</v>
-      </c>
-      <c r="C5" s="26" t="n">
-        <v>46265</v>
+      <c r="B5" s="26">
+        <f>IF(ISNUMBER(_Control!$B$4),_Control!$B$4,IFERROR(DATE(VALUE(MID(_Control!$B$4,1,4)),VALUE(MID(_Control!$B$4,6,2)),VALUE(MID(_Control!$B$4,9,2))),_Control!$B$4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="26">
+        <f>IF(ISNUMBER(_Control!$B$5),_Control!$B$5,IFERROR(DATE(VALUE(MID(_Control!$B$5,1,4)),VALUE(MID(_Control!$B$5,6,2)),VALUE(MID(_Control!$B$5,9,2))),_Control!$B$5))</f>
+        <v/>
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
@@ -57637,6 +58774,172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Current_Start</t>
+        </is>
+      </c>
+      <c r="B2" s="55" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>First day of the period you are reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Current_End</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Last day of the period you are reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Compare_Start</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>First day of the period you are comparing it against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>Compare_End</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Last day of that comparison period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Brand_Name</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>Northwind Supply Co.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Written by the automation so you can tell which client this file is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Last_Refresh</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n"/>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Written by the automation on every refresh. If this is stale the workflow did not run — check the n8n execution log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Rows_Synced</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="n"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Ad-level rows written by the last refresh. Zero means the raw sheet was empty or the column mapping broke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>The automation writes this tab and the two data tabs (Fundamentals, Ad Data) and nothing else. Every other number in the kit is a formula reading these cells, so there is nothing for it to update by hand and no way for a refresh to break a calculation. Do not rename the Key column: the workflow matches rows on it.</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="60" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="60" t="n"/>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="60" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="60" t="n"/>
+      <c r="B12" s="60" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="60" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="60" t="n"/>
+      <c r="B13" s="60" t="n"/>
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="60" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:D13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -57651,13 +58954,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="55">
+      <c r="A1" s="61">
         <f>'Start Here'!C6</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="56">
+      <c r="A2" s="62">
         <f>TEXT('KPI Calc'!$B$4,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$4,"yyyy-mm-dd")&amp;"      vs      "&amp;TEXT('KPI Calc'!$B$5,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$5,"yyyy-mm-dd")</f>
         <v/>
       </c>
@@ -57669,144 +58972,144 @@
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="57" t="inlineStr">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>AD SPEND</t>
         </is>
       </c>
-      <c r="B5" s="58" t="n"/>
-      <c r="C5" s="57" t="inlineStr">
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
-      <c r="D5" s="58" t="n"/>
-      <c r="E5" s="57" t="inlineStr">
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="63" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="F5" s="58" t="n"/>
-      <c r="G5" s="57" t="inlineStr">
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>PROFIT AFTER AD SPEND</t>
         </is>
       </c>
-      <c r="H5" s="58" t="n"/>
+      <c r="H5" s="60" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="59">
+      <c r="A6" s="64">
         <f>'KPI Calc'!B9</f>
         <v/>
       </c>
-      <c r="B6" s="58" t="n"/>
-      <c r="C6" s="59">
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="64">
         <f>'KPI Calc'!B17</f>
         <v/>
       </c>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="60">
+      <c r="D6" s="60" t="n"/>
+      <c r="E6" s="65">
         <f>'KPI Calc'!B30</f>
         <v/>
       </c>
-      <c r="F6" s="58" t="n"/>
-      <c r="G6" s="59">
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="64">
         <f>'KPI Calc'!B36</f>
         <v/>
       </c>
-      <c r="H6" s="58" t="n"/>
+      <c r="H6" s="60" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="A7" s="61">
+      <c r="A7" s="66">
         <f>"vs "&amp;TEXT('KPI Calc'!C9,"#,##0")&amp;" last period"</f>
         <v/>
       </c>
-      <c r="B7" s="58" t="n"/>
-      <c r="C7" s="61">
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="66">
         <f>"vs "&amp;TEXT('KPI Calc'!C17,"#,##0")&amp;" last period"</f>
         <v/>
       </c>
-      <c r="D7" s="58" t="n"/>
-      <c r="E7" s="61">
+      <c r="D7" s="60" t="n"/>
+      <c r="E7" s="66">
         <f>"breakeven "&amp;ROUND('KPI Calc'!B35,2)&amp;"x"</f>
         <v/>
       </c>
-      <c r="F7" s="58" t="n"/>
-      <c r="G7" s="61">
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="66">
         <f>"POAS "&amp;ROUND('KPI Calc'!B37,2)&amp;"x"</f>
         <v/>
       </c>
-      <c r="H7" s="58" t="n"/>
+      <c r="H7" s="60" t="n"/>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="57" t="inlineStr">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>PURCHASES</t>
         </is>
       </c>
-      <c r="B9" s="58" t="n"/>
-      <c r="C9" s="57" t="inlineStr">
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="D9" s="58" t="n"/>
-      <c r="E9" s="57" t="inlineStr">
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="63" t="inlineStr">
         <is>
           <t>COST PER PURCHASE</t>
         </is>
       </c>
-      <c r="F9" s="58" t="n"/>
-      <c r="G9" s="57" t="inlineStr">
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="63" t="inlineStr">
         <is>
           <t>REVENUE / 1,000 IMPRESSIONS</t>
         </is>
       </c>
-      <c r="H9" s="58" t="n"/>
+      <c r="H9" s="60" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="62">
+      <c r="A10" s="67">
         <f>'KPI Calc'!B16</f>
         <v/>
       </c>
-      <c r="B10" s="58" t="n"/>
-      <c r="C10" s="59">
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="64">
         <f>'KPI Calc'!B29</f>
         <v/>
       </c>
-      <c r="D10" s="58" t="n"/>
-      <c r="E10" s="59">
+      <c r="D10" s="60" t="n"/>
+      <c r="E10" s="64">
         <f>'KPI Calc'!B28</f>
         <v/>
       </c>
-      <c r="F10" s="58" t="n"/>
-      <c r="G10" s="59">
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="64">
         <f>'KPI Calc'!B31</f>
         <v/>
       </c>
-      <c r="H10" s="58" t="n"/>
+      <c r="H10" s="60" t="n"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="61">
+      <c r="A11" s="66">
         <f>"vs "&amp;TEXT('KPI Calc'!C16,"#,##0")&amp;" last period"</f>
         <v/>
       </c>
-      <c r="B11" s="58" t="n"/>
-      <c r="C11" s="61">
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="66">
         <f>"vs "&amp;TEXT('KPI Calc'!C29,"#,##0")&amp;" last period"</f>
         <v/>
       </c>
-      <c r="D11" s="58" t="n"/>
-      <c r="E11" s="61">
+      <c r="D11" s="60" t="n"/>
+      <c r="E11" s="66">
         <f>"contribution/order "&amp;TEXT('KPI Calc'!B34/MAX(1,'KPI Calc'!B16),"#,##0")</f>
         <v/>
       </c>
-      <c r="F11" s="58" t="n"/>
-      <c r="G11" s="61">
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="66">
         <f>"CPM "&amp;TEXT('KPI Calc'!B19,"#,##0")</f>
         <v/>
       </c>
-      <c r="H11" s="58" t="n"/>
+      <c r="H11" s="60" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -57823,37 +59126,37 @@
       <c r="H13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="63" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="B14" s="64" t="inlineStr">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="C14" s="64" t="inlineStr">
+      <c r="C14" s="69" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="D14" s="64" t="inlineStr">
+      <c r="D14" s="69" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="E14" s="64" t="inlineStr">
+      <c r="E14" s="69" t="inlineStr">
         <is>
           <t>Purchases</t>
         </is>
       </c>
-      <c r="F14" s="64" t="inlineStr">
+      <c r="F14" s="69" t="inlineStr">
         <is>
           <t>Cost / purchase</t>
         </is>
       </c>
-      <c r="G14" s="64" t="inlineStr">
+      <c r="G14" s="69" t="inlineStr">
         <is>
           <t>Share of spend</t>
         </is>
@@ -57865,31 +59168,31 @@
           <t>Meta</t>
         </is>
       </c>
-      <c r="B15" s="65">
+      <c r="B15" s="70">
         <f>SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
         <v/>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="70">
         <f>SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
         <v/>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="71">
         <f>IFERROR(C15/B15,0)</f>
         <v/>
       </c>
-      <c r="E15" s="67">
+      <c r="E15" s="58">
         <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
         <v/>
       </c>
-      <c r="F15" s="65">
+      <c r="F15" s="70">
         <f>IFERROR(B15/E15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="68">
+      <c r="G15" s="72">
         <f>IFERROR(B15/$B$17,0)</f>
         <v/>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="73">
         <f>REPT("█",ROUND(14*IFERROR(B15/$B$17,0),0))</f>
         <v/>
       </c>
@@ -57900,31 +59203,31 @@
           <t>TikTok</t>
         </is>
       </c>
-      <c r="B16" s="65">
+      <c r="B16" s="70">
         <f>SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
         <v/>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="70">
         <f>SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
         <v/>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="71">
         <f>IFERROR(C16/B16,0)</f>
         <v/>
       </c>
-      <c r="E16" s="67">
+      <c r="E16" s="58">
         <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
         <v/>
       </c>
-      <c r="F16" s="65">
+      <c r="F16" s="70">
         <f>IFERROR(B16/E16,0)</f>
         <v/>
       </c>
-      <c r="G16" s="68">
+      <c r="G16" s="72">
         <f>IFERROR(B16/$B$17,0)</f>
         <v/>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="73">
         <f>REPT("█",ROUND(14*IFERROR(B16/$B$17,0),0))</f>
         <v/>
       </c>
@@ -57935,31 +59238,31 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="74">
         <f>SUM(B15:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="74">
         <f>SUM(C15:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="75">
         <f>IFERROR(C17/B17,0)</f>
         <v/>
       </c>
-      <c r="E17" s="72">
+      <c r="E17" s="76">
         <f>SUM(E15:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="70">
+      <c r="F17" s="74">
         <f>IFERROR(B17/E17,0)</f>
         <v/>
       </c>
-      <c r="G17" s="73">
+      <c r="G17" s="77">
         <f>IFERROR(B17/B17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="74" t="inlineStr"/>
+      <c r="H17" s="78" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -57976,38 +59279,38 @@
       <c r="H19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="63" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B20" s="69" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C20" s="64" t="inlineStr">
+      <c r="C20" s="69" t="inlineStr">
         <is>
           <t>Step rate</t>
         </is>
       </c>
-      <c r="D20" s="64" t="inlineStr">
+      <c r="D20" s="69" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="E20" s="64" t="inlineStr">
+      <c r="E20" s="69" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="64" t="inlineStr">
+      <c r="F20" s="69" t="inlineStr">
         <is>
           <t>Bar</t>
         </is>
       </c>
-      <c r="G20" s="64" t="inlineStr"/>
-      <c r="H20" s="64" t="inlineStr"/>
+      <c r="G20" s="69" t="inlineStr"/>
+      <c r="H20" s="69" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
@@ -58015,14 +59318,14 @@
           <t>Impressions</t>
         </is>
       </c>
-      <c r="B21" s="67">
+      <c r="B21" s="58">
         <f>'KPI Calc'!B10</f>
         <v/>
       </c>
-      <c r="C21" s="75" t="n"/>
-      <c r="D21" s="75" t="n"/>
-      <c r="E21" s="75" t="n"/>
-      <c r="F21" s="75" t="n"/>
+      <c r="C21" s="79" t="n"/>
+      <c r="D21" s="79" t="n"/>
+      <c r="E21" s="79" t="n"/>
+      <c r="F21" s="79" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
@@ -58030,15 +59333,15 @@
           <t>Clicks</t>
         </is>
       </c>
-      <c r="B22" s="67">
+      <c r="B22" s="58">
         <f>'KPI Calc'!B12</f>
         <v/>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="72">
         <f>'KPI Calc'!B21</f>
         <v/>
       </c>
-      <c r="D22" s="76">
+      <c r="D22" s="80">
         <f>Benchmarks!$E$9</f>
         <v/>
       </c>
@@ -58046,7 +59349,7 @@
         <f>IFERROR(INDEX(Benchmarks!$G$7:$G$21,3),"")</f>
         <v/>
       </c>
-      <c r="F22" s="69">
+      <c r="F22" s="73">
         <f>REPT("█",ROUND(20*IFERROR(MIN(1,C22/D22),0),0))</f>
         <v/>
       </c>
@@ -58057,15 +59360,15 @@
           <t>Add to cart</t>
         </is>
       </c>
-      <c r="B23" s="67">
+      <c r="B23" s="58">
         <f>'KPI Calc'!B14</f>
         <v/>
       </c>
-      <c r="C23" s="68">
+      <c r="C23" s="72">
         <f>'KPI Calc'!B23</f>
         <v/>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="80">
         <f>Benchmarks!$E$11</f>
         <v/>
       </c>
@@ -58073,7 +59376,7 @@
         <f>IFERROR(INDEX(Benchmarks!$G$7:$G$21,5),"")</f>
         <v/>
       </c>
-      <c r="F23" s="69">
+      <c r="F23" s="73">
         <f>REPT("█",ROUND(20*IFERROR(MIN(1,C23/D23),0),0))</f>
         <v/>
       </c>
@@ -58084,15 +59387,15 @@
           <t>Initiate checkout</t>
         </is>
       </c>
-      <c r="B24" s="67">
+      <c r="B24" s="58">
         <f>'KPI Calc'!B15</f>
         <v/>
       </c>
-      <c r="C24" s="68">
+      <c r="C24" s="72">
         <f>'KPI Calc'!B24</f>
         <v/>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="80">
         <f>Benchmarks!$E$12</f>
         <v/>
       </c>
@@ -58100,7 +59403,7 @@
         <f>IFERROR(INDEX(Benchmarks!$G$7:$G$21,6),"")</f>
         <v/>
       </c>
-      <c r="F24" s="69">
+      <c r="F24" s="73">
         <f>REPT("█",ROUND(20*IFERROR(MIN(1,C24/D24),0),0))</f>
         <v/>
       </c>
@@ -58111,15 +59414,15 @@
           <t>Purchases</t>
         </is>
       </c>
-      <c r="B25" s="67">
+      <c r="B25" s="58">
         <f>'KPI Calc'!B16</f>
         <v/>
       </c>
-      <c r="C25" s="68">
+      <c r="C25" s="72">
         <f>'KPI Calc'!B25</f>
         <v/>
       </c>
-      <c r="D25" s="76">
+      <c r="D25" s="80">
         <f>Benchmarks!$E$13</f>
         <v/>
       </c>
@@ -58127,7 +59430,7 @@
         <f>IFERROR(INDEX(Benchmarks!$G$7:$G$21,7),"")</f>
         <v/>
       </c>
-      <c r="F25" s="69">
+      <c r="F25" s="73">
         <f>REPT("█",ROUND(20*IFERROR(MIN(1,C25/D25),0),0))</f>
         <v/>
       </c>
@@ -58138,15 +59441,15 @@
           <t>Meta click → landing page</t>
         </is>
       </c>
-      <c r="B26" s="77">
+      <c r="B26" s="81">
         <f>SUMIFS(Fundamentals!$G$2:$G$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4)</f>
         <v/>
       </c>
-      <c r="C26" s="78">
+      <c r="C26" s="82">
         <f>IF(B26=0,"—",'KPI Calc'!B27)</f>
         <v/>
       </c>
-      <c r="D26" s="76">
+      <c r="D26" s="80">
         <f>Benchmarks!$E$10</f>
         <v/>
       </c>
@@ -58154,11 +59457,11 @@
         <f>IFERROR(INDEX(Benchmarks!$G$7:$G$21,4),"")</f>
         <v/>
       </c>
-      <c r="F26" s="69">
+      <c r="F26" s="73">
         <f>REPT("█",ROUND(20*IFERROR(MIN(1,C26/D26),0),0))</f>
         <v/>
       </c>
-      <c r="G26" s="79" t="inlineStr">
+      <c r="G26" s="83" t="inlineStr">
         <is>
           <t>Meta only — TikTok doesn't report landing page views</t>
         </is>
@@ -58179,7 +59482,7 @@
       <c r="H28" s="4" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="80">
+      <c r="A29" s="84">
         <f>"Headline: we spent "&amp;TEXT(ROUND('KPI Calc'!B9,0),"#,##0")&amp;" and returned "&amp;TEXT(ROUND('KPI Calc'!B17,0),"#,##0")&amp;" ("&amp;ROUND('KPI Calc'!B30,2)&amp;"x). "&amp;IF('KPI Calc'!B30&gt;='KPI Calc'!B35,"That is above the "&amp;ROUND('KPI Calc'!B35,2)&amp;"x breakeven, so media paid for itself this period.","That is below the "&amp;ROUND('KPI Calc'!B35,2)&amp;"x breakeven — media did not pay for itself this period and we need to talk about that directly.")</f>
         <v/>
       </c>
@@ -58192,7 +59495,7 @@
       <c r="H29" s="54" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="80">
+      <c r="A30" s="84">
         <f>"Movement: spend "&amp;IF('KPI Calc'!E9&gt;=0,"up","down")&amp;" "&amp;TEXT(ABS('KPI Calc'!E9),"0%")&amp;" while revenue "&amp;IF('KPI Calc'!E17&gt;=0,"rose","fell")&amp;" "&amp;TEXT(ABS('KPI Calc'!E17),"0%")&amp;", so ROAS "&amp;IF('KPI Calc'!B30&gt;='KPI Calc'!C30,"improved","slipped")&amp;" from "&amp;ROUND('KPI Calc'!C30,2)&amp;"x to "&amp;ROUND('KPI Calc'!B30,2)&amp;"x. Costs per thousand impressions went from "&amp;TEXT(ROUND('KPI Calc'!C19,0),"#,##0")&amp;" to "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;"."</f>
         <v/>
       </c>
@@ -58205,7 +59508,7 @@
       <c r="H30" s="54" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="80">
+      <c r="A31" s="84">
         <f>"Where the money went: "&amp;TEXT('Dashboard'!G15,"0%")&amp;" of budget on Meta returning "&amp;ROUND('Dashboard'!D15,2)&amp;"x, and "&amp;TEXT('Dashboard'!G16,"0%")&amp;" on TikTok returning "&amp;ROUND('Dashboard'!D16,2)&amp;"x. "&amp;IF('Dashboard'!D15&gt;'Dashboard'!D16,"Meta is the more efficient channel this period.","TikTok is the more efficient channel this period.")</f>
         <v/>
       </c>
@@ -58218,7 +59521,7 @@
       <c r="H31" s="54" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="80">
+      <c r="A32" s="84">
         <f>"Efficiency read: CPM "&amp;TEXT(ROUND('KPI Calc'!B19,0),"#,##0")&amp;", CTR "&amp;TEXT('KPI Calc'!B21,"0.00%")&amp;", click-to-purchase "&amp;TEXT('KPI Calc'!B26,"0.00%")&amp;", AOV "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". Frequency is "&amp;ROUND('KPI Calc'!B22,2)&amp;", "&amp;IF('KPI Calc'!B22&gt;3.5,"which is high enough that creative fatigue is now a budget risk — fresh assets before we scale.",IF('KPI Calc'!B26&lt;'KPI Calc'!C26*0.85,"which is below the fatigue line, so this is a conversion problem rather than a fatigue one: click-to-purchase fell from "&amp;TEXT('KPI Calc'!C26,"0.00%")&amp;" to "&amp;TEXT('KPI Calc'!B26,"0.00%")&amp;". Fix traffic quality and the landing page before adding budget.","which leaves room to add budget without hitting fatigue."))</f>
         <v/>
       </c>
@@ -58231,7 +59534,7 @@
       <c r="H32" s="54" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="80">
+      <c r="A33" s="84">
         <f>"Cost per purchase is "&amp;TEXT(ROUND('KPI Calc'!B28,0),"#,##0")&amp;" against an AOV of "&amp;TEXT(ROUND('KPI Calc'!B29,0),"#,##0")&amp;". At a "&amp;TEXT('KPI Calc'!B33,"0.0%")&amp;" contribution margin, breakeven ROAS is "&amp;ROUND('KPI Calc'!B35,2)&amp;"x, and headroom before we hit it is roughly "&amp;TEXT(ROUND(MAX(0,'KPI Calc'!B17*'KPI Calc'!B33-'KPI Calc'!B9),0),"#,##0")&amp;" more in spend at today's efficiency."</f>
         <v/>
       </c>
@@ -58287,13 +59590,1664 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="61">
+        <f>'Start Here'!C6&amp;" — Meta"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62">
+        <f>TEXT('KPI Calc'!$B$4,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$4,"yyyy-mm-dd")&amp;"      vs      "&amp;TEXT('KPI Calc'!$B$5,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$5,"yyyy-mm-dd")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25">
+        <f>"Meta only — every figure on this tab is filtered to Meta. TikTok lives on the TikTok Dashboard; the blended view is on the Dashboard tab."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>AD SPEND</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="63" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>PROFIT AFTER AD SPEND</t>
+        </is>
+      </c>
+      <c r="H5" s="60" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="64">
+        <f>SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="64">
+        <f>SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="D6" s="60" t="n"/>
+      <c r="E6" s="65">
+        <f>IFERROR(C6/A6,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="64">
+        <f>IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="60" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1">
+      <c r="A7" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="D7" s="60" t="n"/>
+      <c r="E7" s="66">
+        <f>"breakeven "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x"</f>
+        <v/>
+      </c>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="66">
+        <f>"POAS "&amp;ROUND(IFERROR((C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6)/A6,0),2)&amp;"x"</f>
+        <v/>
+      </c>
+      <c r="H7" s="60" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>PURCHASES</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="63" t="inlineStr">
+        <is>
+          <t>COST PER PURCHASE</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="63" t="inlineStr">
+        <is>
+          <t>REVENUE / 1,000 IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="H9" s="60" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="67">
+        <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="64">
+        <f>IFERROR(C6/B30,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="60" t="n"/>
+      <c r="E10" s="64">
+        <f>IFERROR(A6/B30,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="64">
+        <f>IFERROR(C6/B26*1000,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="60" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="66">
+        <f>"vs "&amp;TEXT(IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="D11" s="60" t="n"/>
+      <c r="E11" s="66">
+        <f>"contribution/order "&amp;TEXT(IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))/MAX(1,B30),0),"#,##0")</f>
+        <v/>
+      </c>
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="66">
+        <f>"CPM "&amp;TEXT(IFERROR(A6/B26*1000,0),"#,##0")</f>
+        <v/>
+      </c>
+      <c r="H11" s="60" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EFFICIENCY  —  Meta only</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B14" s="69" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="D14" s="69" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F14" s="69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="B15" s="70">
+        <f>IFERROR(A6/B26*1000,0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="85">
+        <f>IFERROR(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")*1000,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="86">
+        <f>IFERROR(B15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="85">
+        <f>Benchmarks!$E$7</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
+        <f>IF(N(B15)=0,"—",IF(B15&lt;=Benchmarks!$F$7,"Strong",IF(B15&lt;=Benchmarks!$E$7,"Target",IF(B15&lt;=Benchmarks!$D$7,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="B16" s="70">
+        <f>IFERROR(A6/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="85">
+        <f>IFERROR(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="86">
+        <f>IFERROR(B16/C16-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="85">
+        <f>Benchmarks!$E$8</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>IF(N(B16)=0,"—",IF(B16&lt;=Benchmarks!$F$8,"Strong",IF(B16&lt;=Benchmarks!$E$8,"Target",IF(B16&lt;=Benchmarks!$D$8,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B17" s="72">
+        <f>IFERROR(B27/B26,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="86">
+        <f>IFERROR(B17/C17-1,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="80">
+        <f>Benchmarks!$E$9</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>IF(N(B17)=0,"—",IF(B17&gt;=Benchmarks!$F$9,"Strong",IF(B17&gt;=Benchmarks!$E$9,"Target",IF(B17&gt;=Benchmarks!$D$9,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B18" s="87">
+        <f>IFERROR(B26/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="88">
+        <f>IFERROR(SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="86">
+        <f>IFERROR(B18/C18-1,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="88">
+        <f>Benchmarks!$E$15</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
+        <f>IF(N(B18)=0,"—",IF(B18&lt;=Benchmarks!$F$15,"Strong",IF(B18&lt;=Benchmarks!$E$15,"Target",IF(B18&lt;=Benchmarks!$D$15,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Click to add to cart</t>
+        </is>
+      </c>
+      <c r="B19" s="72">
+        <f>IFERROR(B28/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="86">
+        <f>IFERROR(B19/C19-1,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="80">
+        <f>Benchmarks!$E$11</f>
+        <v/>
+      </c>
+      <c r="F19" s="36">
+        <f>IF(N(B19)=0,"—",IF(B19&gt;=Benchmarks!$F$11,"Strong",IF(B19&gt;=Benchmarks!$E$11,"Target",IF(B19&gt;=Benchmarks!$D$11,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Add to cart to checkout</t>
+        </is>
+      </c>
+      <c r="B20" s="72">
+        <f>IFERROR(B29/B28,0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="86">
+        <f>IFERROR(B20/C20-1,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="80">
+        <f>Benchmarks!$E$12</f>
+        <v/>
+      </c>
+      <c r="F20" s="36">
+        <f>IF(N(B20)=0,"—",IF(B20&gt;=Benchmarks!$F$12,"Strong",IF(B20&gt;=Benchmarks!$E$12,"Target",IF(B20&gt;=Benchmarks!$D$12,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Checkout to purchase</t>
+        </is>
+      </c>
+      <c r="B21" s="72">
+        <f>IFERROR(B30/B29,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="86">
+        <f>IFERROR(B21/C21-1,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="80">
+        <f>Benchmarks!$E$13</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
+        <f>IF(N(B21)=0,"—",IF(B21&gt;=Benchmarks!$F$13,"Strong",IF(B21&gt;=Benchmarks!$E$13,"Target",IF(B21&gt;=Benchmarks!$D$13,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Click to purchase CVR</t>
+        </is>
+      </c>
+      <c r="B22" s="72">
+        <f>IFERROR(B30/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="86">
+        <f>IFERROR(B22/C22-1,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="80">
+        <f>Benchmarks!$E$14</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
+        <f>IF(N(B22)=0,"—",IF(B22&gt;=Benchmarks!$F$14,"Strong",IF(B22&gt;=Benchmarks!$E$14,"Target",IF(B22&gt;=Benchmarks!$D$14,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE FUNNEL  —  Meta</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="68" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>Step rate</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="B26" s="58">
+        <f>SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="C26" s="82">
+        <f>IFERROR(B27/B26,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="80">
+        <f>Benchmarks!$E$9</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>IF(N(C26)=0,"—",IF(C26&gt;=Benchmarks!$F$9,"Strong",IF(C26&gt;=Benchmarks!$E$9,"Target",IF(C26&gt;=Benchmarks!$D$9,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="B27" s="58">
+        <f>SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="C27" s="82">
+        <f>IFERROR(B28/B27,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="80">
+        <f>Benchmarks!$E$11</f>
+        <v/>
+      </c>
+      <c r="E27" s="36">
+        <f>IF(N(C27)=0,"—",IF(C27&gt;=Benchmarks!$F$11,"Strong",IF(C27&gt;=Benchmarks!$E$11,"Target",IF(C27&gt;=Benchmarks!$D$11,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Add to cart</t>
+        </is>
+      </c>
+      <c r="B28" s="58">
+        <f>SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="C28" s="82">
+        <f>IFERROR(B29/B28,0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="80">
+        <f>Benchmarks!$E$12</f>
+        <v/>
+      </c>
+      <c r="E28" s="36">
+        <f>IF(N(C28)=0,"—",IF(C28&gt;=Benchmarks!$F$12,"Strong",IF(C28&gt;=Benchmarks!$E$12,"Target",IF(C28&gt;=Benchmarks!$D$12,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Initiate checkout</t>
+        </is>
+      </c>
+      <c r="B29" s="58">
+        <f>SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="C29" s="82">
+        <f>IFERROR(B30/B29,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="80">
+        <f>Benchmarks!$E$13</f>
+        <v/>
+      </c>
+      <c r="E29" s="36">
+        <f>IF(N(C29)=0,"—",IF(C29&gt;=Benchmarks!$F$13,"Strong",IF(C29&gt;=Benchmarks!$E$13,"Target",IF(C29&gt;=Benchmarks!$D$13,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Purchases</t>
+        </is>
+      </c>
+      <c r="B30" s="58">
+        <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>Meta click → landing page</t>
+        </is>
+      </c>
+      <c r="B31" s="81">
+        <f>SUMIFS(Fundamentals!$G$2:$G$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
+        <v/>
+      </c>
+      <c r="C31" s="82">
+        <f>IF(B31=0,"—",IFERROR(B31/B27,0))</f>
+        <v/>
+      </c>
+      <c r="D31" s="80">
+        <f>Benchmarks!$E$10</f>
+        <v/>
+      </c>
+      <c r="E31" s="36">
+        <f>IF(N(C31)=0,"—",IF(C31&gt;=Benchmarks!$F$10,"Strong",IF(C31&gt;=Benchmarks!$E$10,"Target",IF(C31&gt;=Benchmarks!$D$10,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROFITABILITY  —  same cost model as the other tabs</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Contribution margin %</t>
+        </is>
+      </c>
+      <c r="B35" s="72">
+        <f>IFERROR(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30),0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="83" t="inlineStr">
+        <is>
+          <t>Revenue left after COGS, fees and shipping, per order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>Breakeven ROAS</t>
+        </is>
+      </c>
+      <c r="B36" s="71">
+        <f>IFERROR(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="83" t="inlineStr">
+        <is>
+          <t>Below this, this platform loses money on every sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>Target ROAS (from Benchmarks)</t>
+        </is>
+      </c>
+      <c r="B37" s="71">
+        <f>Benchmarks!$E$18</f>
+        <v/>
+      </c>
+      <c r="C37" s="83" t="inlineStr">
+        <is>
+          <t>Change it on the Benchmarks tab once you know the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>Profit after ad spend</t>
+        </is>
+      </c>
+      <c r="B38" s="70">
+        <f>IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="83" t="inlineStr">
+        <is>
+          <t>Contribution minus what this platform cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>POAS (profit on ad spend)</t>
+        </is>
+      </c>
+      <c r="B39" s="71">
+        <f>IFERROR(B38/A6,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>Profit per unit of spend. The number to move once ROAS clears breakeven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT TO SAY ABOUT META  —  generated, edit before sending</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="84">
+        <f>"Meta took "&amp;TEXT(IFERROR(A6/'KPI Calc'!B9,0),"0%")&amp;" of the budget, spent "&amp;TEXT(ROUND(A6,0),"#,##0")&amp;" and returned "&amp;TEXT(ROUND(C6,0),"#,##0")&amp;" ("&amp;ROUND(IFERROR(C6/A6,0),2)&amp;"x). "&amp;IF(IFERROR(C6/A6,0)&gt;=1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),"Above its "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x breakeven, so this platform paid for itself.","Below its "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x breakeven — this platform did not pay for itself this period.")</f>
+        <v/>
+      </c>
+      <c r="B42" s="54" t="n"/>
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="54" t="n"/>
+      <c r="F42" s="54" t="n"/>
+      <c r="G42" s="54" t="n"/>
+      <c r="H42" s="54" t="n"/>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="84">
+        <f>"Movement: spend "&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")=0,"had no comparison",IF(A6&gt;=SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),"up","down"))&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")=0,""," "&amp;TEXT(ABS(IFERROR(A6/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")-1,0)),"0%"))&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")=0,""," while revenue "&amp;IF(C6&gt;=SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),"rose","fell")&amp;" "&amp;TEXT(ABS(IFERROR(C6/SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")-1,0)),"0%"))&amp;", so ROAS "&amp;IF(IFERROR(C6/A6,0)&gt;=IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0),"improved","slipped")&amp;" from "&amp;ROUND(IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0),2)&amp;"x to "&amp;ROUND(IFERROR(C6/A6,0),2)&amp;"x."</f>
+        <v/>
+      </c>
+      <c r="B43" s="54" t="n"/>
+      <c r="C43" s="54" t="n"/>
+      <c r="D43" s="54" t="n"/>
+      <c r="E43" s="54" t="n"/>
+      <c r="F43" s="54" t="n"/>
+      <c r="G43" s="54" t="n"/>
+      <c r="H43" s="54" t="n"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="84">
+        <f>"Read: CPM "&amp;TEXT(ROUND(IFERROR(A6/B26*1000,0),0),"#,##0")&amp;", CTR "&amp;TEXT(IFERROR(B27/B26,0),"0.00%")&amp;", click-to-purchase "&amp;TEXT(IFERROR(B30/B27,0),"0.00%")&amp;", frequency "&amp;ROUND(IFERROR(B26/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"Meta"),2),2)&amp;". "&amp;IF(IFERROR(B30/B27,0)&lt;IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)*0.85,"Conversion on paid clicks fell versus the comparison period, so the drop is in traffic quality or the landing page, not in delivery.","Delivery and conversion are both holding steady.")</f>
+        <v/>
+      </c>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="54" t="n"/>
+      <c r="F44" s="54" t="n"/>
+      <c r="G44" s="54" t="n"/>
+      <c r="H44" s="54" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="84">
+        <f>"Biggest lever: "&amp;IF(IFERROR(B30/B27,0)&lt;IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"Meta"),0)*0.85,"the click-to-purchase step — fix the landing page and traffic before adding budget here.",IF(IFERROR(A6/B26*1000,0)&gt;Benchmarks!$E$7,"CPM. This platform is paying above target for attention.","scaling the winners: efficiency is inside target, so more budget should still clear breakeven."))</f>
+        <v/>
+      </c>
+      <c r="B45" s="54" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="54" t="n"/>
+      <c r="F45" s="54" t="n"/>
+      <c r="G45" s="54" t="n"/>
+      <c r="H45" s="54" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F15:F22">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>F15="Strong"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>F15="Target"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="4">
+      <formula>F15="Watch"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>F15="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E30">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>E26="Strong"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>E26="Target"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="4">
+      <formula>E26="Watch"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E26="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="61">
+        <f>'Start Here'!C6&amp;" — TikTok"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62">
+        <f>TEXT('KPI Calc'!$B$4,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$4,"yyyy-mm-dd")&amp;"      vs      "&amp;TEXT('KPI Calc'!$B$5,"yyyy-mm-dd")&amp;" → "&amp;TEXT('KPI Calc'!$C$5,"yyyy-mm-dd")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25">
+        <f>"TikTok only — every figure on this tab is filtered to TikTok. Meta lives on the Meta Dashboard; the blended view is on the Dashboard tab."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="63" t="inlineStr">
+        <is>
+          <t>AD SPEND</t>
+        </is>
+      </c>
+      <c r="B5" s="60" t="n"/>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="63" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="F5" s="60" t="n"/>
+      <c r="G5" s="63" t="inlineStr">
+        <is>
+          <t>PROFIT AFTER AD SPEND</t>
+        </is>
+      </c>
+      <c r="H5" s="60" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="64">
+        <f>SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="B6" s="60" t="n"/>
+      <c r="C6" s="64">
+        <f>SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="D6" s="60" t="n"/>
+      <c r="E6" s="65">
+        <f>IFERROR(C6/A6,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="60" t="n"/>
+      <c r="G6" s="64">
+        <f>IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="60" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1">
+      <c r="A7" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="B7" s="60" t="n"/>
+      <c r="C7" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="D7" s="60" t="n"/>
+      <c r="E7" s="66">
+        <f>"breakeven "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x"</f>
+        <v/>
+      </c>
+      <c r="F7" s="60" t="n"/>
+      <c r="G7" s="66">
+        <f>"POAS "&amp;ROUND(IFERROR((C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6)/A6,0),2)&amp;"x"</f>
+        <v/>
+      </c>
+      <c r="H7" s="60" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
+        <is>
+          <t>PURCHASES</t>
+        </is>
+      </c>
+      <c r="B9" s="60" t="n"/>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="D9" s="60" t="n"/>
+      <c r="E9" s="63" t="inlineStr">
+        <is>
+          <t>COST PER PURCHASE</t>
+        </is>
+      </c>
+      <c r="F9" s="60" t="n"/>
+      <c r="G9" s="63" t="inlineStr">
+        <is>
+          <t>REVENUE / 1,000 IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="H9" s="60" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="67">
+        <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="64">
+        <f>IFERROR(C6/B30,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="60" t="n"/>
+      <c r="E10" s="64">
+        <f>IFERROR(A6/B30,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="64">
+        <f>IFERROR(C6/B26*1000,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="60" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="66">
+        <f>"vs "&amp;TEXT(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="B11" s="60" t="n"/>
+      <c r="C11" s="66">
+        <f>"vs "&amp;TEXT(IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0),"#,##0")&amp;" last period"</f>
+        <v/>
+      </c>
+      <c r="D11" s="60" t="n"/>
+      <c r="E11" s="66">
+        <f>"contribution/order "&amp;TEXT(IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))/MAX(1,B30),0),"#,##0")</f>
+        <v/>
+      </c>
+      <c r="F11" s="60" t="n"/>
+      <c r="G11" s="66">
+        <f>"CPM "&amp;TEXT(IFERROR(A6/B26*1000,0),"#,##0")</f>
+        <v/>
+      </c>
+      <c r="H11" s="60" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EFFICIENCY  —  TikTok only</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B14" s="69" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="inlineStr">
+        <is>
+          <t>Compare</t>
+        </is>
+      </c>
+      <c r="D14" s="69" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F14" s="69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="B15" s="70">
+        <f>IFERROR(A6/B26*1000,0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="85">
+        <f>IFERROR(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")*1000,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="86">
+        <f>IFERROR(B15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E15" s="85">
+        <f>Benchmarks!$E$7</f>
+        <v/>
+      </c>
+      <c r="F15" s="36">
+        <f>IF(N(B15)=0,"—",IF(B15&lt;=Benchmarks!$F$7,"Strong",IF(B15&lt;=Benchmarks!$E$7,"Target",IF(B15&lt;=Benchmarks!$D$7,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>CPC</t>
+        </is>
+      </c>
+      <c r="B16" s="70">
+        <f>IFERROR(A6/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="85">
+        <f>IFERROR(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="86">
+        <f>IFERROR(B16/C16-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="85">
+        <f>Benchmarks!$E$8</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>IF(N(B16)=0,"—",IF(B16&lt;=Benchmarks!$F$8,"Strong",IF(B16&lt;=Benchmarks!$E$8,"Target",IF(B16&lt;=Benchmarks!$D$8,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B17" s="72">
+        <f>IFERROR(B27/B26,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="86">
+        <f>IFERROR(B17/C17-1,"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="80">
+        <f>Benchmarks!$E$9</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>IF(N(B17)=0,"—",IF(B17&gt;=Benchmarks!$F$9,"Strong",IF(B17&gt;=Benchmarks!$E$9,"Target",IF(B17&gt;=Benchmarks!$D$9,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B18" s="87">
+        <f>IFERROR(B26/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="88">
+        <f>IFERROR(SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="86">
+        <f>IFERROR(B18/C18-1,"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="88">
+        <f>Benchmarks!$E$15</f>
+        <v/>
+      </c>
+      <c r="F18" s="36">
+        <f>IF(N(B18)=0,"—",IF(B18&lt;=Benchmarks!$F$15,"Strong",IF(B18&lt;=Benchmarks!$E$15,"Target",IF(B18&lt;=Benchmarks!$D$15,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Click to add to cart</t>
+        </is>
+      </c>
+      <c r="B19" s="72">
+        <f>IFERROR(B28/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D19" s="86">
+        <f>IFERROR(B19/C19-1,"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="80">
+        <f>Benchmarks!$E$11</f>
+        <v/>
+      </c>
+      <c r="F19" s="36">
+        <f>IF(N(B19)=0,"—",IF(B19&gt;=Benchmarks!$F$11,"Strong",IF(B19&gt;=Benchmarks!$E$11,"Target",IF(B19&gt;=Benchmarks!$D$11,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Add to cart to checkout</t>
+        </is>
+      </c>
+      <c r="B20" s="72">
+        <f>IFERROR(B29/B28,0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="86">
+        <f>IFERROR(B20/C20-1,"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="80">
+        <f>Benchmarks!$E$12</f>
+        <v/>
+      </c>
+      <c r="F20" s="36">
+        <f>IF(N(B20)=0,"—",IF(B20&gt;=Benchmarks!$F$12,"Strong",IF(B20&gt;=Benchmarks!$E$12,"Target",IF(B20&gt;=Benchmarks!$D$12,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Checkout to purchase</t>
+        </is>
+      </c>
+      <c r="B21" s="72">
+        <f>IFERROR(B30/B29,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="86">
+        <f>IFERROR(B21/C21-1,"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="80">
+        <f>Benchmarks!$E$13</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
+        <f>IF(N(B21)=0,"—",IF(B21&gt;=Benchmarks!$F$13,"Strong",IF(B21&gt;=Benchmarks!$E$13,"Target",IF(B21&gt;=Benchmarks!$D$13,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Click to purchase CVR</t>
+        </is>
+      </c>
+      <c r="B22" s="72">
+        <f>IFERROR(B30/B27,0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="80">
+        <f>IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="86">
+        <f>IFERROR(B22/C22-1,"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="80">
+        <f>Benchmarks!$E$14</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
+        <f>IF(N(B22)=0,"—",IF(B22&gt;=Benchmarks!$F$14,"Strong",IF(B22&gt;=Benchmarks!$E$14,"Target",IF(B22&gt;=Benchmarks!$D$14,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE FUNNEL  —  TikTok</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="68" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>Step rate</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="B26" s="58">
+        <f>SUMIFS(Fundamentals!$D$2:$D$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="C26" s="82">
+        <f>IFERROR(B27/B26,0)</f>
+        <v/>
+      </c>
+      <c r="D26" s="80">
+        <f>Benchmarks!$E$9</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>IF(N(C26)=0,"—",IF(C26&gt;=Benchmarks!$F$9,"Strong",IF(C26&gt;=Benchmarks!$E$9,"Target",IF(C26&gt;=Benchmarks!$D$9,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="B27" s="58">
+        <f>SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="C27" s="82">
+        <f>IFERROR(B28/B27,0)</f>
+        <v/>
+      </c>
+      <c r="D27" s="80">
+        <f>Benchmarks!$E$11</f>
+        <v/>
+      </c>
+      <c r="E27" s="36">
+        <f>IF(N(C27)=0,"—",IF(C27&gt;=Benchmarks!$F$11,"Strong",IF(C27&gt;=Benchmarks!$E$11,"Target",IF(C27&gt;=Benchmarks!$D$11,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Add to cart</t>
+        </is>
+      </c>
+      <c r="B28" s="58">
+        <f>SUMIFS(Fundamentals!$H$2:$H$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="C28" s="82">
+        <f>IFERROR(B29/B28,0)</f>
+        <v/>
+      </c>
+      <c r="D28" s="80">
+        <f>Benchmarks!$E$12</f>
+        <v/>
+      </c>
+      <c r="E28" s="36">
+        <f>IF(N(C28)=0,"—",IF(C28&gt;=Benchmarks!$F$12,"Strong",IF(C28&gt;=Benchmarks!$E$12,"Target",IF(C28&gt;=Benchmarks!$D$12,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Initiate checkout</t>
+        </is>
+      </c>
+      <c r="B29" s="58">
+        <f>SUMIFS(Fundamentals!$I$2:$I$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+      <c r="C29" s="82">
+        <f>IFERROR(B30/B29,0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="80">
+        <f>Benchmarks!$E$13</f>
+        <v/>
+      </c>
+      <c r="E29" s="36">
+        <f>IF(N(C29)=0,"—",IF(C29&gt;=Benchmarks!$F$13,"Strong",IF(C29&gt;=Benchmarks!$E$13,"Target",IF(C29&gt;=Benchmarks!$D$13,"Watch","Weak"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Purchases</t>
+        </is>
+      </c>
+      <c r="B30" s="58">
+        <f>SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>Landing page views</t>
+        </is>
+      </c>
+      <c r="B31" s="79" t="inlineStr">
+        <is>
+          <t>not reported</t>
+        </is>
+      </c>
+      <c r="C31" s="83" t="inlineStr">
+        <is>
+          <t>TikTok does not report landing page views — the funnel starts at clicks for this platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PROFITABILITY  —  same cost model as the other tabs</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Contribution margin %</t>
+        </is>
+      </c>
+      <c r="B35" s="72">
+        <f>IFERROR(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30),0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="83" t="inlineStr">
+        <is>
+          <t>Revenue left after COGS, fees and shipping, per order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>Breakeven ROAS</t>
+        </is>
+      </c>
+      <c r="B36" s="71">
+        <f>IFERROR(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="83" t="inlineStr">
+        <is>
+          <t>Below this, this platform loses money on every sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>Target ROAS (from Benchmarks)</t>
+        </is>
+      </c>
+      <c r="B37" s="71">
+        <f>Benchmarks!$E$18</f>
+        <v/>
+      </c>
+      <c r="C37" s="83" t="inlineStr">
+        <is>
+          <t>Change it on the Benchmarks tab once you know the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>Profit after ad spend</t>
+        </is>
+      </c>
+      <c r="B38" s="70">
+        <f>IFERROR(C6*(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30))-A6,0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="83" t="inlineStr">
+        <is>
+          <t>Contribution minus what this platform cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>POAS (profit on ad spend)</t>
+        </is>
+      </c>
+      <c r="B39" s="71">
+        <f>IFERROR(B38/A6,0)</f>
+        <v/>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>Profit per unit of spend. The number to move once ROAS clears breakeven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT TO SAY ABOUT TIKTOK  —  generated, edit before sending</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="84">
+        <f>"TikTok took "&amp;TEXT(IFERROR(A6/'KPI Calc'!B9,0),"0%")&amp;" of the budget, spent "&amp;TEXT(ROUND(A6,0),"#,##0")&amp;" and returned "&amp;TEXT(ROUND(C6,0),"#,##0")&amp;" ("&amp;ROUND(IFERROR(C6/A6,0),2)&amp;"x). "&amp;IF(IFERROR(C6/A6,0)&gt;=1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),"Above its "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x breakeven, so this platform paid for itself.","Below its "&amp;ROUND(1/(1-'KPI Calc'!$J$5-'KPI Calc'!$J$6-'KPI Calc'!$J$7/(C6/B30)),2)&amp;"x breakeven — this platform did not pay for itself this period.")</f>
+        <v/>
+      </c>
+      <c r="B42" s="54" t="n"/>
+      <c r="C42" s="54" t="n"/>
+      <c r="D42" s="54" t="n"/>
+      <c r="E42" s="54" t="n"/>
+      <c r="F42" s="54" t="n"/>
+      <c r="G42" s="54" t="n"/>
+      <c r="H42" s="54" t="n"/>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="84">
+        <f>"Movement: spend "&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")=0,"had no comparison",IF(A6&gt;=SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),"up","down"))&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")=0,""," "&amp;TEXT(ABS(IFERROR(A6/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")-1,0)),"0%"))&amp;IF(SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")=0,""," while revenue "&amp;IF(C6&gt;=SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),"rose","fell")&amp;" "&amp;TEXT(ABS(IFERROR(C6/SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")-1,0)),"0%"))&amp;", so ROAS "&amp;IF(IFERROR(C6/A6,0)&gt;=IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0),"improved","slipped")&amp;" from "&amp;ROUND(IFERROR(SUMIFS(Fundamentals!$K$2:$K$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$C$2:$C$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0),2)&amp;"x to "&amp;ROUND(IFERROR(C6/A6,0),2)&amp;"x."</f>
+        <v/>
+      </c>
+      <c r="B43" s="54" t="n"/>
+      <c r="C43" s="54" t="n"/>
+      <c r="D43" s="54" t="n"/>
+      <c r="E43" s="54" t="n"/>
+      <c r="F43" s="54" t="n"/>
+      <c r="G43" s="54" t="n"/>
+      <c r="H43" s="54" t="n"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="84">
+        <f>"Read: CPM "&amp;TEXT(ROUND(IFERROR(A6/B26*1000,0),0),"#,##0")&amp;", CTR "&amp;TEXT(IFERROR(B27/B26,0),"0.00%")&amp;", click-to-purchase "&amp;TEXT(IFERROR(B30/B27,0),"0.00%")&amp;", frequency "&amp;ROUND(IFERROR(B26/SUMIFS(Fundamentals!$E$2:$E$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$4,Fundamentals!$B$2:$B$6000,"TikTok"),2),2)&amp;". "&amp;IF(IFERROR(B30/B27,0)&lt;IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)*0.85,"Conversion on paid clicks fell versus the comparison period, so the drop is in traffic quality or the landing page, not in delivery.","Delivery and conversion are both holding steady.")</f>
+        <v/>
+      </c>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="54" t="n"/>
+      <c r="F44" s="54" t="n"/>
+      <c r="G44" s="54" t="n"/>
+      <c r="H44" s="54" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="84">
+        <f>"Biggest lever: "&amp;IF(IFERROR(B30/B27,0)&lt;IFERROR(SUMIFS(Fundamentals!$J$2:$J$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok")/SUMIFS(Fundamentals!$F$2:$F$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;$B$5,Fundamentals!$A$2:$A$6000,"&lt;="&amp;$C$5,Fundamentals!$B$2:$B$6000,"TikTok"),0)*0.85,"the click-to-purchase step — fix the landing page and traffic before adding budget here.",IF(IFERROR(A6/B26*1000,0)&gt;Benchmarks!$E$7,"CPM. This platform is paying above target for attention.","scaling the winners: efficiency is inside target, so more budget should still clear breakeven."))</f>
+        <v/>
+      </c>
+      <c r="B45" s="54" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="54" t="n"/>
+      <c r="E45" s="54" t="n"/>
+      <c r="F45" s="54" t="n"/>
+      <c r="G45" s="54" t="n"/>
+      <c r="H45" s="54" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:H9"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F15:F22">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>F15="Strong"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="3">
+      <formula>F15="Target"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="4">
+      <formula>F15="Watch"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>F15="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E26:E30">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>E26="Strong"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="3">
+      <formula>E26="Target"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="4">
+      <formula>E26="Watch"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>E26="Weak"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -58322,7 +61276,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>Ranked by spend. One row per ad name — edit column A when you paste your own data.</t>
+          <t>Ranked by spend inside the selected period. Column A fills itself from Ad Data — you never type an ad name here.</t>
         </is>
       </c>
     </row>
@@ -58334,1916 +61288,1502 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="63" t="inlineStr">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>Ad Name</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="B5" s="69" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="C5" s="63" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>Campaign</t>
         </is>
       </c>
-      <c r="D5" s="63" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>Creative Key</t>
         </is>
       </c>
-      <c r="E5" s="64" t="inlineStr">
+      <c r="E5" s="69" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="F5" s="64" t="inlineStr">
+      <c r="F5" s="69" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G5" s="64" t="inlineStr">
+      <c r="G5" s="69" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="H5" s="64" t="inlineStr">
+      <c r="H5" s="69" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="I5" s="64" t="inlineStr">
+      <c r="I5" s="69" t="inlineStr">
         <is>
           <t>Purchases</t>
         </is>
       </c>
-      <c r="J5" s="64" t="inlineStr">
+      <c r="J5" s="69" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="K5" s="64" t="inlineStr">
+      <c r="K5" s="69" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="L5" s="64" t="inlineStr">
+      <c r="L5" s="69" t="inlineStr">
         <is>
           <t>Cost / purchase</t>
         </is>
       </c>
-      <c r="M5" s="64" t="inlineStr">
+      <c r="M5" s="69" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="N5" s="63" t="inlineStr">
+      <c r="N5" s="68" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>VID | Founder story | v4</t>
-        </is>
-      </c>
-      <c r="B6" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>UGC-Founder</t>
-        </is>
-      </c>
-      <c r="E6" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F6" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G6" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H6" s="78">
-        <f>IFERROR(G6/F6,0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J6" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K6" s="66">
-        <f>IFERROR(J6/E6,0)</f>
-        <v/>
-      </c>
-      <c r="L6" s="82">
-        <f>IFERROR(E6/I6,0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="82">
-        <f>IFERROR(J6/I6,0)</f>
+      <c r="A6" s="17">
+        <f>IFERROR(QUERY('Ad Data'!$A$2:$K$1500,"select C where C is not null and A &gt;= date'"&amp;TEXT('KPI Calc'!$B$4,"yyyy-mm-dd")&amp;"' and A &lt;= date'"&amp;TEXT('KPI Calc'!$C$4,"yyyy-mm-dd")&amp;"' group by C order by sum(G) desc label sum(G) '' limit 25",0),"")</f>
+        <v/>
+      </c>
+      <c r="B6" s="89">
+        <f>IF($A6="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A6,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A6,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A6,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E6" s="90">
+        <f>IF($A6="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F6" s="81">
+        <f>IF($A6="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G6" s="81">
+        <f>IF($A6="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H6" s="82">
+        <f>IF($A6="","",IFERROR(G6/F6,0))</f>
+        <v/>
+      </c>
+      <c r="I6" s="81">
+        <f>IF($A6="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J6" s="90">
+        <f>IF($A6="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A6,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K6" s="71">
+        <f>IF($A6="","",IFERROR(J6/E6,0))</f>
+        <v/>
+      </c>
+      <c r="L6" s="90">
+        <f>IF($A6="","",IFERROR(E6/I6,0))</f>
+        <v/>
+      </c>
+      <c r="M6" s="90">
+        <f>IF($A6="","",IFERROR(J6/I6,0))</f>
         <v/>
       </c>
       <c r="N6" s="11">
-        <f>IF(E6=0,"No spend in period",IF(K6&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K6&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A6="","",IF(E6=0,"No spend in period",IF(K6&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K6&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>STATIC | Bundle offer | v2</t>
-        </is>
-      </c>
-      <c r="B7" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Static-Bundle</t>
-        </is>
-      </c>
-      <c r="E7" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F7" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G7" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H7" s="78">
-        <f>IFERROR(G7/F7,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J7" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K7" s="66">
-        <f>IFERROR(J7/E7,0)</f>
-        <v/>
-      </c>
-      <c r="L7" s="82">
-        <f>IFERROR(E7/I7,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="82">
-        <f>IFERROR(J7/I7,0)</f>
+      <c r="A7" s="17" t="n"/>
+      <c r="B7" s="89">
+        <f>IF($A7="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A7,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A7,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A7,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E7" s="90">
+        <f>IF($A7="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F7" s="81">
+        <f>IF($A7="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G7" s="81">
+        <f>IF($A7="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H7" s="82">
+        <f>IF($A7="","",IFERROR(G7/F7,0))</f>
+        <v/>
+      </c>
+      <c r="I7" s="81">
+        <f>IF($A7="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J7" s="90">
+        <f>IF($A7="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A7,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K7" s="71">
+        <f>IF($A7="","",IFERROR(J7/E7,0))</f>
+        <v/>
+      </c>
+      <c r="L7" s="90">
+        <f>IF($A7="","",IFERROR(E7/I7,0))</f>
+        <v/>
+      </c>
+      <c r="M7" s="90">
+        <f>IF($A7="","",IFERROR(J7/I7,0))</f>
         <v/>
       </c>
       <c r="N7" s="11">
-        <f>IF(E7=0,"No spend in period",IF(K7&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K7&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A7="","",IF(E7=0,"No spend in period",IF(K7&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K7&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>VID | Founder story | v3</t>
-        </is>
-      </c>
-      <c r="B8" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>UGC-Founder</t>
-        </is>
-      </c>
-      <c r="E8" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F8" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G8" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H8" s="78">
-        <f>IFERROR(G8/F8,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J8" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K8" s="66">
-        <f>IFERROR(J8/E8,0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="82">
-        <f>IFERROR(E8/I8,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="82">
-        <f>IFERROR(J8/I8,0)</f>
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="89">
+        <f>IF($A8="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A8,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A8,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A8,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="90">
+        <f>IF($A8="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F8" s="81">
+        <f>IF($A8="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G8" s="81">
+        <f>IF($A8="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H8" s="82">
+        <f>IF($A8="","",IFERROR(G8/F8,0))</f>
+        <v/>
+      </c>
+      <c r="I8" s="81">
+        <f>IF($A8="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J8" s="90">
+        <f>IF($A8="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A8,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K8" s="71">
+        <f>IF($A8="","",IFERROR(J8/E8,0))</f>
+        <v/>
+      </c>
+      <c r="L8" s="90">
+        <f>IF($A8="","",IFERROR(E8/I8,0))</f>
+        <v/>
+      </c>
+      <c r="M8" s="90">
+        <f>IF($A8="","",IFERROR(J8/I8,0))</f>
         <v/>
       </c>
       <c r="N8" s="11">
-        <f>IF(E8=0,"No spend in period",IF(K8&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K8&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A8="","",IF(E8=0,"No spend in period",IF(K8&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K8&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>VID | Review compilation | v1</t>
-        </is>
-      </c>
-      <c r="B9" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Interest | EG</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>UGC-Reviews</t>
-        </is>
-      </c>
-      <c r="E9" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F9" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G9" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H9" s="78">
-        <f>IFERROR(G9/F9,0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J9" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K9" s="66">
-        <f>IFERROR(J9/E9,0)</f>
-        <v/>
-      </c>
-      <c r="L9" s="82">
-        <f>IFERROR(E9/I9,0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="82">
-        <f>IFERROR(J9/I9,0)</f>
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="89">
+        <f>IF($A9="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A9,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A9,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A9,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="90">
+        <f>IF($A9="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F9" s="81">
+        <f>IF($A9="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G9" s="81">
+        <f>IF($A9="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H9" s="82">
+        <f>IF($A9="","",IFERROR(G9/F9,0))</f>
+        <v/>
+      </c>
+      <c r="I9" s="81">
+        <f>IF($A9="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J9" s="90">
+        <f>IF($A9="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A9,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K9" s="71">
+        <f>IF($A9="","",IFERROR(J9/E9,0))</f>
+        <v/>
+      </c>
+      <c r="L9" s="90">
+        <f>IF($A9="","",IFERROR(E9/I9,0))</f>
+        <v/>
+      </c>
+      <c r="M9" s="90">
+        <f>IF($A9="","",IFERROR(J9/I9,0))</f>
         <v/>
       </c>
       <c r="N9" s="11">
-        <f>IF(E9=0,"No spend in period",IF(K9&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K9&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A9="","",IF(E9=0,"No spend in period",IF(K9&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K9&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>STATIC | Bundle offer | v1</t>
-        </is>
-      </c>
-      <c r="B10" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Test | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Static-Bundle</t>
-        </is>
-      </c>
-      <c r="E10" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F10" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G10" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H10" s="78">
-        <f>IFERROR(G10/F10,0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J10" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K10" s="66">
-        <f>IFERROR(J10/E10,0)</f>
-        <v/>
-      </c>
-      <c r="L10" s="82">
-        <f>IFERROR(E10/I10,0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="82">
-        <f>IFERROR(J10/I10,0)</f>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="89">
+        <f>IF($A10="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A10,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A10,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A10,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="90">
+        <f>IF($A10="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F10" s="81">
+        <f>IF($A10="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G10" s="81">
+        <f>IF($A10="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H10" s="82">
+        <f>IF($A10="","",IFERROR(G10/F10,0))</f>
+        <v/>
+      </c>
+      <c r="I10" s="81">
+        <f>IF($A10="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J10" s="90">
+        <f>IF($A10="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A10,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K10" s="71">
+        <f>IF($A10="","",IFERROR(J10/E10,0))</f>
+        <v/>
+      </c>
+      <c r="L10" s="90">
+        <f>IF($A10="","",IFERROR(E10/I10,0))</f>
+        <v/>
+      </c>
+      <c r="M10" s="90">
+        <f>IF($A10="","",IFERROR(J10/I10,0))</f>
         <v/>
       </c>
       <c r="N10" s="11">
-        <f>IF(E10=0,"No spend in period",IF(K10&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K10&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A10="","",IF(E10=0,"No spend in period",IF(K10&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K10&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>STATIC | Discount 20% | v1</t>
-        </is>
-      </c>
-      <c r="B11" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Retargeting | 7d IC</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Static-Discount</t>
-        </is>
-      </c>
-      <c r="E11" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F11" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G11" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H11" s="78">
-        <f>IFERROR(G11/F11,0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J11" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K11" s="66">
-        <f>IFERROR(J11/E11,0)</f>
-        <v/>
-      </c>
-      <c r="L11" s="82">
-        <f>IFERROR(E11/I11,0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="82">
-        <f>IFERROR(J11/I11,0)</f>
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="89">
+        <f>IF($A11="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A11,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A11,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A11,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="90">
+        <f>IF($A11="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F11" s="81">
+        <f>IF($A11="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G11" s="81">
+        <f>IF($A11="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H11" s="82">
+        <f>IF($A11="","",IFERROR(G11/F11,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="81">
+        <f>IF($A11="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J11" s="90">
+        <f>IF($A11="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A11,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K11" s="71">
+        <f>IF($A11="","",IFERROR(J11/E11,0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="90">
+        <f>IF($A11="","",IFERROR(E11/I11,0))</f>
+        <v/>
+      </c>
+      <c r="M11" s="90">
+        <f>IF($A11="","",IFERROR(J11/I11,0))</f>
         <v/>
       </c>
       <c r="N11" s="11">
-        <f>IF(E11=0,"No spend in period",IF(K11&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K11&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A11="","",IF(E11=0,"No spend in period",IF(K11&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K11&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>CAROUSEL | Best sellers</t>
-        </is>
-      </c>
-      <c r="B12" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Retargeting | 14d ATC</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Carousel-Bestsellers</t>
-        </is>
-      </c>
-      <c r="E12" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F12" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G12" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H12" s="78">
-        <f>IFERROR(G12/F12,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J12" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K12" s="66">
-        <f>IFERROR(J12/E12,0)</f>
-        <v/>
-      </c>
-      <c r="L12" s="82">
-        <f>IFERROR(E12/I12,0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="82">
-        <f>IFERROR(J12/I12,0)</f>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="89">
+        <f>IF($A12="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A12,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A12,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A12,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="90">
+        <f>IF($A12="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F12" s="81">
+        <f>IF($A12="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G12" s="81">
+        <f>IF($A12="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H12" s="82">
+        <f>IF($A12="","",IFERROR(G12/F12,0))</f>
+        <v/>
+      </c>
+      <c r="I12" s="81">
+        <f>IF($A12="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J12" s="90">
+        <f>IF($A12="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A12,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K12" s="71">
+        <f>IF($A12="","",IFERROR(J12/E12,0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="90">
+        <f>IF($A12="","",IFERROR(E12/I12,0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="90">
+        <f>IF($A12="","",IFERROR(J12/I12,0))</f>
         <v/>
       </c>
       <c r="N12" s="11">
-        <f>IF(E12=0,"No spend in period",IF(K12&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K12&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A12="","",IF(E12=0,"No spend in period",IF(K12&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K12&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>VID | Founder story | v1</t>
-        </is>
-      </c>
-      <c r="B13" s="81" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>UGC-Founder</t>
-        </is>
-      </c>
-      <c r="E13" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F13" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G13" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H13" s="78">
-        <f>IFERROR(G13/F13,0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J13" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K13" s="66">
-        <f>IFERROR(J13/E13,0)</f>
-        <v/>
-      </c>
-      <c r="L13" s="82">
-        <f>IFERROR(E13/I13,0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="82">
-        <f>IFERROR(J13/I13,0)</f>
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="89">
+        <f>IF($A13="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A13,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A13,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A13,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="90">
+        <f>IF($A13="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F13" s="81">
+        <f>IF($A13="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G13" s="81">
+        <f>IF($A13="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H13" s="82">
+        <f>IF($A13="","",IFERROR(G13/F13,0))</f>
+        <v/>
+      </c>
+      <c r="I13" s="81">
+        <f>IF($A13="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J13" s="90">
+        <f>IF($A13="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A13,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K13" s="71">
+        <f>IF($A13="","",IFERROR(J13/E13,0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="90">
+        <f>IF($A13="","",IFERROR(E13/I13,0))</f>
+        <v/>
+      </c>
+      <c r="M13" s="90">
+        <f>IF($A13="","",IFERROR(J13/I13,0))</f>
         <v/>
       </c>
       <c r="N13" s="11">
-        <f>IF(E13=0,"No spend in period",IF(K13&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K13&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A13="","",IF(E13=0,"No spend in period",IF(K13&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K13&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>UGC | Problem-solution | v2</t>
-        </is>
-      </c>
-      <c r="B14" s="81" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>TT-UGC-ProbSol</t>
-        </is>
-      </c>
-      <c r="E14" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F14" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G14" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H14" s="78">
-        <f>IFERROR(G14/F14,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J14" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K14" s="66">
-        <f>IFERROR(J14/E14,0)</f>
-        <v/>
-      </c>
-      <c r="L14" s="82">
-        <f>IFERROR(E14/I14,0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="82">
-        <f>IFERROR(J14/I14,0)</f>
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="89">
+        <f>IF($A14="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A14,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A14,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A14,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="90">
+        <f>IF($A14="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F14" s="81">
+        <f>IF($A14="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G14" s="81">
+        <f>IF($A14="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H14" s="82">
+        <f>IF($A14="","",IFERROR(G14/F14,0))</f>
+        <v/>
+      </c>
+      <c r="I14" s="81">
+        <f>IF($A14="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J14" s="90">
+        <f>IF($A14="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A14,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K14" s="71">
+        <f>IF($A14="","",IFERROR(J14/E14,0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="90">
+        <f>IF($A14="","",IFERROR(E14/I14,0))</f>
+        <v/>
+      </c>
+      <c r="M14" s="90">
+        <f>IF($A14="","",IFERROR(J14/I14,0))</f>
         <v/>
       </c>
       <c r="N14" s="11">
-        <f>IF(E14=0,"No spend in period",IF(K14&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K14&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A14="","",IF(E14=0,"No spend in period",IF(K14&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K14&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>UGC | Trend audio | v1</t>
-        </is>
-      </c>
-      <c r="B15" s="81" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>TT-UGC-Trend</t>
-        </is>
-      </c>
-      <c r="E15" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F15" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G15" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H15" s="78">
-        <f>IFERROR(G15/F15,0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J15" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K15" s="66">
-        <f>IFERROR(J15/E15,0)</f>
-        <v/>
-      </c>
-      <c r="L15" s="82">
-        <f>IFERROR(E15/I15,0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="82">
-        <f>IFERROR(J15/I15,0)</f>
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="89">
+        <f>IF($A15="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A15,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A15,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A15,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="90">
+        <f>IF($A15="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F15" s="81">
+        <f>IF($A15="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G15" s="81">
+        <f>IF($A15="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H15" s="82">
+        <f>IF($A15="","",IFERROR(G15/F15,0))</f>
+        <v/>
+      </c>
+      <c r="I15" s="81">
+        <f>IF($A15="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J15" s="90">
+        <f>IF($A15="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A15,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K15" s="71">
+        <f>IF($A15="","",IFERROR(J15/E15,0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="90">
+        <f>IF($A15="","",IFERROR(E15/I15,0))</f>
+        <v/>
+      </c>
+      <c r="M15" s="90">
+        <f>IF($A15="","",IFERROR(J15/I15,0))</f>
         <v/>
       </c>
       <c r="N15" s="11">
-        <f>IF(E15=0,"No spend in period",IF(K15&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K15&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A15="","",IF(E15=0,"No spend in period",IF(K15&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K15&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>UGC | Trend audio | v2</t>
-        </is>
-      </c>
-      <c r="B16" s="81" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Prospecting | Broad | EG</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>TT-UGC-Trend</t>
-        </is>
-      </c>
-      <c r="E16" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F16" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G16" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H16" s="78">
-        <f>IFERROR(G16/F16,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J16" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K16" s="66">
-        <f>IFERROR(J16/E16,0)</f>
-        <v/>
-      </c>
-      <c r="L16" s="82">
-        <f>IFERROR(E16/I16,0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="82">
-        <f>IFERROR(J16/I16,0)</f>
+      <c r="A16" s="17" t="n"/>
+      <c r="B16" s="89">
+        <f>IF($A16="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A16,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A16,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A16,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="90">
+        <f>IF($A16="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F16" s="81">
+        <f>IF($A16="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G16" s="81">
+        <f>IF($A16="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H16" s="82">
+        <f>IF($A16="","",IFERROR(G16/F16,0))</f>
+        <v/>
+      </c>
+      <c r="I16" s="81">
+        <f>IF($A16="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J16" s="90">
+        <f>IF($A16="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A16,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K16" s="71">
+        <f>IF($A16="","",IFERROR(J16/E16,0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="90">
+        <f>IF($A16="","",IFERROR(E16/I16,0))</f>
+        <v/>
+      </c>
+      <c r="M16" s="90">
+        <f>IF($A16="","",IFERROR(J16/I16,0))</f>
         <v/>
       </c>
       <c r="N16" s="11">
-        <f>IF(E16=0,"No spend in period",IF(K16&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K16&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A16="","",IF(E16=0,"No spend in period",IF(K16&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K16&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Spark ad | Creator A</t>
-        </is>
-      </c>
-      <c r="B17" s="81" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Spark | Creator A</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>TT-Spark-CreatorA</t>
-        </is>
-      </c>
-      <c r="E17" s="82">
-        <f>SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="F17" s="77">
-        <f>SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="G17" s="77">
-        <f>SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="H17" s="78">
-        <f>IFERROR(G17/F17,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="77">
-        <f>SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="J17" s="82">
-        <f>SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="K17" s="66">
-        <f>IFERROR(J17/E17,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="82">
-        <f>IFERROR(E17/I17,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="82">
-        <f>IFERROR(J17/I17,0)</f>
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="89">
+        <f>IF($A17="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A17,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A17,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A17,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="90">
+        <f>IF($A17="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F17" s="81">
+        <f>IF($A17="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G17" s="81">
+        <f>IF($A17="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H17" s="82">
+        <f>IF($A17="","",IFERROR(G17/F17,0))</f>
+        <v/>
+      </c>
+      <c r="I17" s="81">
+        <f>IF($A17="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J17" s="90">
+        <f>IF($A17="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A17,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K17" s="71">
+        <f>IF($A17="","",IFERROR(J17/E17,0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="90">
+        <f>IF($A17="","",IFERROR(E17/I17,0))</f>
+        <v/>
+      </c>
+      <c r="M17" s="90">
+        <f>IF($A17="","",IFERROR(J17/I17,0))</f>
         <v/>
       </c>
       <c r="N17" s="11">
-        <f>IF(E17=0,"No spend in period",IF(K17&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K17&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it")))</f>
+        <f>IF($A17="","",IF(E17=0,"No spend in period",IF(K17&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K17&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr"/>
-      <c r="B18" s="81" t="n"/>
-      <c r="C18" s="11" t="inlineStr"/>
-      <c r="D18" s="11" t="inlineStr"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="89">
+        <f>IF($A18="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A18,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A18,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A18,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="90">
+        <f>IF($A18="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A18,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F18" s="81">
+        <f>IF($A18="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A18,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G18" s="81">
+        <f>IF($A18="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A18,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H18" s="82">
+        <f>IF($A18="","",IFERROR(G18/F18,0))</f>
+        <v/>
+      </c>
+      <c r="I18" s="81">
+        <f>IF($A18="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A18,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J18" s="90">
+        <f>IF($A18="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A18,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K18" s="71">
+        <f>IF($A18="","",IFERROR(J18/E18,0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="90">
+        <f>IF($A18="","",IFERROR(E18/I18,0))</f>
+        <v/>
+      </c>
+      <c r="M18" s="90">
+        <f>IF($A18="","",IFERROR(J18/I18,0))</f>
+        <v/>
+      </c>
+      <c r="N18" s="11">
+        <f>IF($A18="","",IF(E18=0,"No spend in period",IF(K18&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K18&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="89">
+        <f>IF($A19="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A19,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A19,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A19,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="90">
+        <f>IF($A19="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A19,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F19" s="81">
+        <f>IF($A19="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A19,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G19" s="81">
+        <f>IF($A19="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A19,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H19" s="82">
+        <f>IF($A19="","",IFERROR(G19/F19,0))</f>
+        <v/>
+      </c>
+      <c r="I19" s="81">
+        <f>IF($A19="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A19,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J19" s="90">
+        <f>IF($A19="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A19,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K19" s="71">
+        <f>IF($A19="","",IFERROR(J19/E19,0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="90">
+        <f>IF($A19="","",IFERROR(E19/I19,0))</f>
+        <v/>
+      </c>
+      <c r="M19" s="90">
+        <f>IF($A19="","",IFERROR(J19/I19,0))</f>
+        <v/>
+      </c>
+      <c r="N19" s="11">
+        <f>IF($A19="","",IF(E19=0,"No spend in period",IF(K19&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K19&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="89">
+        <f>IF($A20="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A20,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A20,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A20,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="90">
+        <f>IF($A20="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A20,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F20" s="81">
+        <f>IF($A20="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A20,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G20" s="81">
+        <f>IF($A20="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A20,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H20" s="82">
+        <f>IF($A20="","",IFERROR(G20/F20,0))</f>
+        <v/>
+      </c>
+      <c r="I20" s="81">
+        <f>IF($A20="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A20,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J20" s="90">
+        <f>IF($A20="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A20,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K20" s="71">
+        <f>IF($A20="","",IFERROR(J20/E20,0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="90">
+        <f>IF($A20="","",IFERROR(E20/I20,0))</f>
+        <v/>
+      </c>
+      <c r="M20" s="90">
+        <f>IF($A20="","",IFERROR(J20/I20,0))</f>
+        <v/>
+      </c>
+      <c r="N20" s="11">
+        <f>IF($A20="","",IF(E20=0,"No spend in period",IF(K20&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K20&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="89">
+        <f>IF($A21="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A21,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A21,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A21,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="90">
+        <f>IF($A21="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A21,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F21" s="81">
+        <f>IF($A21="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A21,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G21" s="81">
+        <f>IF($A21="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A21,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H21" s="82">
+        <f>IF($A21="","",IFERROR(G21/F21,0))</f>
+        <v/>
+      </c>
+      <c r="I21" s="81">
+        <f>IF($A21="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A21,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J21" s="90">
+        <f>IF($A21="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A21,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K21" s="71">
+        <f>IF($A21="","",IFERROR(J21/E21,0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="90">
+        <f>IF($A21="","",IFERROR(E21/I21,0))</f>
+        <v/>
+      </c>
+      <c r="M21" s="90">
+        <f>IF($A21="","",IFERROR(J21/I21,0))</f>
+        <v/>
+      </c>
+      <c r="N21" s="11">
+        <f>IF($A21="","",IF(E21=0,"No spend in period",IF(K21&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K21&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="89">
+        <f>IF($A22="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A22,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A22,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A22,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="90">
+        <f>IF($A22="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A22,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F22" s="81">
+        <f>IF($A22="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A22,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G22" s="81">
+        <f>IF($A22="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A22,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H22" s="82">
+        <f>IF($A22="","",IFERROR(G22/F22,0))</f>
+        <v/>
+      </c>
+      <c r="I22" s="81">
+        <f>IF($A22="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A22,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J22" s="90">
+        <f>IF($A22="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A22,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K22" s="71">
+        <f>IF($A22="","",IFERROR(J22/E22,0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="90">
+        <f>IF($A22="","",IFERROR(E22/I22,0))</f>
+        <v/>
+      </c>
+      <c r="M22" s="90">
+        <f>IF($A22="","",IFERROR(J22/I22,0))</f>
+        <v/>
+      </c>
+      <c r="N22" s="11">
+        <f>IF($A22="","",IF(E22=0,"No spend in period",IF(K22&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K22&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="89">
+        <f>IF($A23="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A23,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A23,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A23,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="90">
+        <f>IF($A23="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A23,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F23" s="81">
+        <f>IF($A23="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A23,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G23" s="81">
+        <f>IF($A23="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A23,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H23" s="82">
+        <f>IF($A23="","",IFERROR(G23/F23,0))</f>
+        <v/>
+      </c>
+      <c r="I23" s="81">
+        <f>IF($A23="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A23,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J23" s="90">
+        <f>IF($A23="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A23,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K23" s="71">
+        <f>IF($A23="","",IFERROR(J23/E23,0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="90">
+        <f>IF($A23="","",IFERROR(E23/I23,0))</f>
+        <v/>
+      </c>
+      <c r="M23" s="90">
+        <f>IF($A23="","",IFERROR(J23/I23,0))</f>
+        <v/>
+      </c>
+      <c r="N23" s="11">
+        <f>IF($A23="","",IF(E23=0,"No spend in period",IF(K23&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K23&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="89">
+        <f>IF($A24="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A24,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A24,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A24,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="90">
+        <f>IF($A24="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A24,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F24" s="81">
+        <f>IF($A24="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A24,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G24" s="81">
+        <f>IF($A24="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A24,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H24" s="82">
+        <f>IF($A24="","",IFERROR(G24/F24,0))</f>
+        <v/>
+      </c>
+      <c r="I24" s="81">
+        <f>IF($A24="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A24,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J24" s="90">
+        <f>IF($A24="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A24,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K24" s="71">
+        <f>IF($A24="","",IFERROR(J24/E24,0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="90">
+        <f>IF($A24="","",IFERROR(E24/I24,0))</f>
+        <v/>
+      </c>
+      <c r="M24" s="90">
+        <f>IF($A24="","",IFERROR(J24/I24,0))</f>
+        <v/>
+      </c>
+      <c r="N24" s="11">
+        <f>IF($A24="","",IF(E24=0,"No spend in period",IF(K24&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K24&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="89">
+        <f>IF($A25="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A25,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A25,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A25,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="90">
+        <f>IF($A25="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A25,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F25" s="81">
+        <f>IF($A25="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A25,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G25" s="81">
+        <f>IF($A25="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A25,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H25" s="82">
+        <f>IF($A25="","",IFERROR(G25/F25,0))</f>
+        <v/>
+      </c>
+      <c r="I25" s="81">
+        <f>IF($A25="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A25,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J25" s="90">
+        <f>IF($A25="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A25,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K25" s="71">
+        <f>IF($A25="","",IFERROR(J25/E25,0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="90">
+        <f>IF($A25="","",IFERROR(E25/I25,0))</f>
+        <v/>
+      </c>
+      <c r="M25" s="90">
+        <f>IF($A25="","",IFERROR(J25/I25,0))</f>
+        <v/>
+      </c>
+      <c r="N25" s="11">
+        <f>IF($A25="","",IF(E25=0,"No spend in period",IF(K25&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K25&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="89">
+        <f>IF($A26="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A26,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A26,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A26,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="90">
+        <f>IF($A26="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A26,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F26" s="81">
+        <f>IF($A26="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A26,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G26" s="81">
+        <f>IF($A26="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A26,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H26" s="82">
+        <f>IF($A26="","",IFERROR(G26/F26,0))</f>
+        <v/>
+      </c>
+      <c r="I26" s="81">
+        <f>IF($A26="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A26,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J26" s="90">
+        <f>IF($A26="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A26,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K26" s="71">
+        <f>IF($A26="","",IFERROR(J26/E26,0))</f>
+        <v/>
+      </c>
+      <c r="L26" s="90">
+        <f>IF($A26="","",IFERROR(E26/I26,0))</f>
+        <v/>
+      </c>
+      <c r="M26" s="90">
+        <f>IF($A26="","",IFERROR(J26/I26,0))</f>
+        <v/>
+      </c>
+      <c r="N26" s="11">
+        <f>IF($A26="","",IF(E26=0,"No spend in period",IF(K26&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K26&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="89">
+        <f>IF($A27="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A27,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A27,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A27,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="90">
+        <f>IF($A27="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A27,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F27" s="81">
+        <f>IF($A27="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A27,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G27" s="81">
+        <f>IF($A27="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A27,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H27" s="82">
+        <f>IF($A27="","",IFERROR(G27/F27,0))</f>
+        <v/>
+      </c>
+      <c r="I27" s="81">
+        <f>IF($A27="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A27,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J27" s="90">
+        <f>IF($A27="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A27,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K27" s="71">
+        <f>IF($A27="","",IFERROR(J27/E27,0))</f>
+        <v/>
+      </c>
+      <c r="L27" s="90">
+        <f>IF($A27="","",IFERROR(E27/I27,0))</f>
+        <v/>
+      </c>
+      <c r="M27" s="90">
+        <f>IF($A27="","",IFERROR(J27/I27,0))</f>
+        <v/>
+      </c>
+      <c r="N27" s="11">
+        <f>IF($A27="","",IF(E27=0,"No spend in period",IF(K27&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K27&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="89">
+        <f>IF($A28="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A28,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A28,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A28,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="90">
+        <f>IF($A28="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A28,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F28" s="81">
+        <f>IF($A28="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A28,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G28" s="81">
+        <f>IF($A28="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A28,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H28" s="82">
+        <f>IF($A28="","",IFERROR(G28/F28,0))</f>
+        <v/>
+      </c>
+      <c r="I28" s="81">
+        <f>IF($A28="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A28,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J28" s="90">
+        <f>IF($A28="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A28,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K28" s="71">
+        <f>IF($A28="","",IFERROR(J28/E28,0))</f>
+        <v/>
+      </c>
+      <c r="L28" s="90">
+        <f>IF($A28="","",IFERROR(E28/I28,0))</f>
+        <v/>
+      </c>
+      <c r="M28" s="90">
+        <f>IF($A28="","",IFERROR(J28/I28,0))</f>
+        <v/>
+      </c>
+      <c r="N28" s="11">
+        <f>IF($A28="","",IF(E28=0,"No spend in period",IF(K28&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K28&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="89">
+        <f>IF($A29="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A29,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A29,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A29,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="90">
+        <f>IF($A29="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A29,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F29" s="81">
+        <f>IF($A29="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A29,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G29" s="81">
+        <f>IF($A29="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A29,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H29" s="82">
+        <f>IF($A29="","",IFERROR(G29/F29,0))</f>
+        <v/>
+      </c>
+      <c r="I29" s="81">
+        <f>IF($A29="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A29,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J29" s="90">
+        <f>IF($A29="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A29,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K29" s="71">
+        <f>IF($A29="","",IFERROR(J29/E29,0))</f>
+        <v/>
+      </c>
+      <c r="L29" s="90">
+        <f>IF($A29="","",IFERROR(E29/I29,0))</f>
+        <v/>
+      </c>
+      <c r="M29" s="90">
+        <f>IF($A29="","",IFERROR(J29/I29,0))</f>
+        <v/>
+      </c>
+      <c r="N29" s="11">
+        <f>IF($A29="","",IF(E29=0,"No spend in period",IF(K29&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K29&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="89">
+        <f>IF($A30="","",IFERROR(INDEX('Ad Data'!$B$2:$B$1500,MATCH($A30,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX('Ad Data'!$D$2:$D$1500,MATCH($A30,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX('Ad Data'!$F$2:$F$1500,MATCH($A30,'Ad Data'!$C$2:$C$1500,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="90">
+        <f>IF($A30="","",SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$C$2:$C$6000,$A30,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="F30" s="81">
+        <f>IF($A30="","",SUMIFS('Ad Data'!$H$2:$H$6000,'Ad Data'!$C$2:$C$6000,$A30,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="G30" s="81">
+        <f>IF($A30="","",SUMIFS('Ad Data'!$I$2:$I$6000,'Ad Data'!$C$2:$C$6000,$A30,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="H30" s="82">
+        <f>IF($A30="","",IFERROR(G30/F30,0))</f>
+        <v/>
+      </c>
+      <c r="I30" s="81">
+        <f>IF($A30="","",SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$C$2:$C$6000,$A30,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="J30" s="90">
+        <f>IF($A30="","",SUMIFS('Ad Data'!$K$2:$K$6000,'Ad Data'!$C$2:$C$6000,$A30,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4))</f>
+        <v/>
+      </c>
+      <c r="K30" s="71">
+        <f>IF($A30="","",IFERROR(J30/E30,0))</f>
+        <v/>
+      </c>
+      <c r="L30" s="90">
+        <f>IF($A30="","",IFERROR(E30/I30,0))</f>
+        <v/>
+      </c>
+      <c r="M30" s="90">
+        <f>IF($A30="","",IFERROR(J30/I30,0))</f>
+        <v/>
+      </c>
+      <c r="N30" s="11">
+        <f>IF($A30="","",IF(E30=0,"No spend in period",IF(K30&gt;=MAX('KPI Calc'!$B$35*1.3,0.01),"Scale — put more budget here",IF(K30&gt;='KPI Calc'!$B$35,"Working — maintain and refresh creative","Below breakeven — fix the page or cut it"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="91">
+        <f>"This table ranks on the period selected in _Control, not on lifetime spend. An ad that burned budget last month but nothing this period drops off; a new winner appears. That is the point — a scaling decision made on lifetime totals is made on the wrong window."</f>
+        <v/>
+      </c>
+      <c r="B32" s="60" t="n"/>
+      <c r="C32" s="60" t="n"/>
+      <c r="D32" s="60" t="n"/>
+      <c r="E32" s="60" t="n"/>
+      <c r="F32" s="60" t="n"/>
+      <c r="G32" s="60" t="n"/>
+      <c r="H32" s="60" t="n"/>
+      <c r="I32" s="60" t="n"/>
+      <c r="J32" s="60" t="n"/>
+      <c r="K32" s="60" t="n"/>
+      <c r="L32" s="60" t="n"/>
+      <c r="M32" s="60" t="n"/>
+      <c r="N32" s="60" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <autoFilter ref="A5:N30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A32:N32"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="N6:N18">
+  <conditionalFormatting sqref="N6:N30">
     <cfRule type="expression" priority="1" dxfId="3">
-      <formula>ISNUMBER(SEARCH("Scale",$N6))</formula>
+      <formula>EXACT($N6,"Scale — put more budget here")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="5">
-      <formula>ISNUMBER(SEARCH("Working",$N6))</formula>
+      <formula>EXACT($N6,"Working — maintain and refresh creative")</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>ISNUMBER(SEARCH("Below breakeven",$N6))</formula>
+      <formula>EXACT($N6,"Below breakeven — fix the page or cut it")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="6">
+      <formula>EXACT($N6,"No spend in period")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K18">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="2"/>
-        <cfvo type="num" val="5"/>
-        <color rgb="00FEE2E2"/>
-        <color rgb="00FEF3C7"/>
-        <color rgb="00DCFCE7"/>
-      </colorScale>
+  <conditionalFormatting sqref="K6:K30">
+    <cfRule type="expression" priority="5" dxfId="7">
+      <formula>AND($K6&lt;&gt;"",$K6&gt;='KPI Calc'!$B$35)</formula>
     </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>These thresholds decide every Status column in the kit. Retune them per account.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>All amounts in EGP. Change the currency label on 'Start Here' after you copy this file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="83" t="inlineStr">
-        <is>
-          <t>⚠ The starting numbers below are placeholders so the status columns work on day one — they are not industry truth. Replace them with this client's own trailing 90-day range by month three. A benchmark you didn't measure is a guess, and clients can smell a guess.   •   Once you have replaced them, type TUNED in cell B28 below so Health Check stops flagging this tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6">
-      <c r="A6" s="63" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B6" s="64" t="inlineStr">
-        <is>
-          <t>Your value</t>
-        </is>
-      </c>
-      <c r="C6" s="64" t="inlineStr">
-        <is>
-          <t>Weak</t>
-        </is>
-      </c>
-      <c r="D6" s="64" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="E6" s="64" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="F6" s="64" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="G6" s="64" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H6" s="63" t="inlineStr">
-        <is>
-          <t>If it's below target, look here first</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>CPM</t>
-        </is>
-      </c>
-      <c r="B7" s="65">
-        <f>'KPI Calc'!B19</f>
-        <v/>
-      </c>
-      <c r="C7" s="84" t="n">
-        <v>140</v>
-      </c>
-      <c r="D7" s="84" t="n">
-        <v>95</v>
-      </c>
-      <c r="E7" s="84" t="n">
-        <v>72</v>
-      </c>
-      <c r="F7" s="84" t="n">
-        <v>55</v>
-      </c>
-      <c r="G7" s="36">
-        <f>IF($B7=0,"—",IF($B7&lt;=F7,"Strong",IF($B7&lt;=E7,"Target",IF($B7&lt;=D7,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H7" s="37" t="inlineStr">
-        <is>
-          <t>Auction pressure, audience saturation, or broad targeting diluting the mix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>CPC</t>
-        </is>
-      </c>
-      <c r="B8" s="65">
-        <f>'KPI Calc'!B20</f>
-        <v/>
-      </c>
-      <c r="C8" s="84" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="84" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E8" s="84" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="84" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G8" s="36">
-        <f>IF($B8=0,"—",IF($B8&lt;=F8,"Strong",IF($B8&lt;=E8,"Target",IF($B8&lt;=D8,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>Mostly CPM plus CTR. If CPC is high but CTR is fine, look at placement and audience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="B9" s="68">
-        <f>'KPI Calc'!B21</f>
-        <v/>
-      </c>
-      <c r="C9" s="76" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="D9" s="76" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="E9" s="76" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F9" s="76" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="G9" s="36">
-        <f>IF($B9=0,"—",IF($B9&gt;=F9,"Strong",IF($B9&gt;=E9,"Target",IF($B9&gt;=D9,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H9" s="37" t="inlineStr">
-        <is>
-          <t>The creative hook — first 3 seconds of video, first line of primary text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Meta click to landing page</t>
-        </is>
-      </c>
-      <c r="B10" s="68">
-        <f>'KPI Calc'!B27</f>
-        <v/>
-      </c>
-      <c r="C10" s="76" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D10" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E10" s="76" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F10" s="76" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G10" s="36">
-        <f>IF($B10=0,"—",IF($B10&gt;=F10,"Strong",IF($B10&gt;=E10,"Target",IF($B10&gt;=D10,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H10" s="37" t="inlineStr">
-        <is>
-          <t>Page speed and mobile load. A technical problem wearing a media costume.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>Click to add to cart</t>
-        </is>
-      </c>
-      <c r="B11" s="68">
-        <f>'KPI Calc'!B23</f>
-        <v/>
-      </c>
-      <c r="C11" s="76" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D11" s="76" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E11" s="76" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F11" s="76" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G11" s="36">
-        <f>IF($B11=0,"—",IF($B11&gt;=F11,"Strong",IF($B11&gt;=E11,"Target",IF($B11&gt;=D11,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H11" s="37" t="inlineStr">
-        <is>
-          <t>Product page: price positioning, imagery, reviews, delivery promise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>Add to cart to checkout</t>
-        </is>
-      </c>
-      <c r="B12" s="68">
-        <f>'KPI Calc'!B24</f>
-        <v/>
-      </c>
-      <c r="C12" s="76" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D12" s="76" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E12" s="76" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F12" s="76" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G12" s="36">
-        <f>IF($B12=0,"—",IF($B12&gt;=F12,"Strong",IF($B12&gt;=E12,"Target",IF($B12&gt;=D12,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H12" s="37" t="inlineStr">
-        <is>
-          <t>Shipping cost, surprise fees, forced account creation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Checkout to purchase</t>
-        </is>
-      </c>
-      <c r="B13" s="68">
-        <f>'KPI Calc'!B25</f>
-        <v/>
-      </c>
-      <c r="C13" s="76" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D13" s="76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="76" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F13" s="76" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G13" s="36">
-        <f>IF($B13=0,"—",IF($B13&gt;=F13,"Strong",IF($B13&gt;=E13,"Target",IF($B13&gt;=D13,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H13" s="37" t="inlineStr">
-        <is>
-          <t>Payment methods, cash on delivery, trust badges, retargeting coverage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Click to purchase CVR</t>
-        </is>
-      </c>
-      <c r="B14" s="68">
-        <f>'KPI Calc'!B26</f>
-        <v/>
-      </c>
-      <c r="C14" s="76" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="D14" s="76" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E14" s="76" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F14" s="76" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G14" s="36">
-        <f>IF($B14=0,"—",IF($B14&gt;=F14,"Strong",IF($B14&gt;=E14,"Target",IF($B14&gt;=D14,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H14" s="37" t="inlineStr">
-        <is>
-          <t>End-to-end site conversion on paid clicks. Compare to this account's own history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="B15" s="85">
-        <f>'KPI Calc'!B22</f>
-        <v/>
-      </c>
-      <c r="C15" s="86" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="86" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E15" s="86" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F15" s="86" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G15" s="36">
-        <f>IF($B15=0,"—",IF($B15&lt;=F15,"Strong",IF($B15&lt;=E15,"Target",IF($B15&lt;=D15,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H15" s="37" t="inlineStr">
-        <is>
-          <t>Creative fatigue. Above target, refresh assets before adding budget.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>AOV</t>
-        </is>
-      </c>
-      <c r="B16" s="65">
-        <f>'KPI Calc'!B29</f>
-        <v/>
-      </c>
-      <c r="C16" s="84" t="n">
-        <v>450</v>
-      </c>
-      <c r="D16" s="84" t="n">
-        <v>550</v>
-      </c>
-      <c r="E16" s="84" t="n">
-        <v>650</v>
-      </c>
-      <c r="F16" s="84" t="n">
-        <v>800</v>
-      </c>
-      <c r="G16" s="36">
-        <f>IF($B16=0,"—",IF($B16&gt;=F16,"Strong",IF($B16&gt;=E16,"Target",IF($B16&gt;=D16,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H16" s="37" t="inlineStr">
-        <is>
-          <t>Placeholder ladder — replace with this account's own trailing range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>Revenue per 1,000 impressions</t>
-        </is>
-      </c>
-      <c r="B17" s="65">
-        <f>'KPI Calc'!B31</f>
-        <v/>
-      </c>
-      <c r="C17" s="84" t="n">
-        <v>80</v>
-      </c>
-      <c r="D17" s="84" t="n">
-        <v>120</v>
-      </c>
-      <c r="E17" s="84" t="n">
-        <v>170</v>
-      </c>
-      <c r="F17" s="84" t="n">
-        <v>250</v>
-      </c>
-      <c r="G17" s="36">
-        <f>IF($B17=0,"—",IF($B17&gt;=F17,"Strong",IF($B17&gt;=E17,"Target",IF($B17&gt;=D17,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H17" s="37" t="inlineStr">
-        <is>
-          <t>The cleanest single measure of end-to-end media efficiency.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>ROAS</t>
-        </is>
-      </c>
-      <c r="B18" s="66">
-        <f>'KPI Calc'!B30</f>
-        <v/>
-      </c>
-      <c r="C18" s="87" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D18" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="87" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F18" s="87" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G18" s="36">
-        <f>IF($B18=0,"—",IF($B18&gt;=F18,"Strong",IF($B18&gt;=E18,"Target",IF($B18&gt;=D18,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H18" s="37" t="inlineStr">
-        <is>
-          <t>Never set a target below breakeven ROAS. Weak here sits below breakeven on purpose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>Breakeven ROAS</t>
-        </is>
-      </c>
-      <c r="B19" s="66">
-        <f>'KPI Calc'!B35</f>
-        <v/>
-      </c>
-      <c r="C19" s="87" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="87" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E19" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="87" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G19" s="36">
-        <f>IF($B19=0,"—",IF($B19&lt;=F19,"Strong",IF($B19&lt;=E19,"Target",IF($B19&lt;=D19,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H19" s="37" t="inlineStr">
-        <is>
-          <t>Calculated from the client's own margin inputs. Do not overwrite this row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>POAS (profit on ad spend)</t>
-        </is>
-      </c>
-      <c r="B20" s="66">
-        <f>'KPI Calc'!B37</f>
-        <v/>
-      </c>
-      <c r="C20" s="87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="87" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E20" s="87" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F20" s="87" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G20" s="36">
-        <f>IF($B20=0,"—",IF($B20&gt;=F20,"Strong",IF($B20&gt;=E20,"Target",IF($B20&gt;=D20,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H20" s="37" t="inlineStr">
-        <is>
-          <t>Profit per unit of spend. The number to move once ROAS is acceptable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Contribution margin %</t>
-        </is>
-      </c>
-      <c r="B21" s="68">
-        <f>'KPI Calc'!B33</f>
-        <v/>
-      </c>
-      <c r="C21" s="76" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D21" s="76" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E21" s="76" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F21" s="76" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G21" s="36">
-        <f>IF($B21=0,"—",IF($B21&gt;=F21,"Strong",IF($B21&gt;=E21,"Target",IF($B21&gt;=D21,"Watch","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="H21" s="37" t="inlineStr">
-        <is>
-          <t>Driven by the client's cost inputs on KPI Calc, cells J5:J7.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="88" t="inlineStr">
-        <is>
-          <t>How status is decided</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="89" t="inlineStr">
-        <is>
-          <t>Higher is better (CTR, rates, AOV, ROAS, POAS): Strong ≥ F, Target ≥ E, Watch ≥ D, otherwise Weak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="89" t="inlineStr">
-        <is>
-          <t>Lower is better (CPM, CPC, Frequency, Breakeven ROAS): the same ladder, mirrored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Benchmarks tuning status</t>
-        </is>
-      </c>
-      <c r="B28" s="90" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Type TUNED here once the thresholds above are this client's own 90-day numbers.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:H5"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G7:G21">
-    <cfRule type="expression" priority="1" dxfId="3">
-      <formula>$G7="Strong"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>$G7="Target"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="4">
-      <formula>$G7="Watch"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
-      <formula>$G7="Weak"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>Health Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>Run this before anything goes to a client. Data errors look exactly like performance problems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DATA COVERAGE</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT COUNTS AS 'GOOD'</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>Rows in the current period</t>
-        </is>
-      </c>
-      <c r="B6" s="67">
-        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)</f>
-        <v/>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>Zero here means your date cells and your data don't overlap. Start here.</t>
-        </is>
-      </c>
-      <c r="E6" s="91" t="inlineStr">
-        <is>
-          <t>There is no universal good CPM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>Distinct days present</t>
-        </is>
-      </c>
-      <c r="B7" s="67">
-        <f>SUMPRODUCT((COUNTIFS(Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)&gt;0)/COUNTIF(Fundamentals!$A$2:$A$6000,Fundamentals!$A$2:$A$6000&amp;""))</f>
-        <v/>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>Should roughly equal the days in your period, per platform.</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>A CPM of 180 EGP is excellent for one category and fatal for another. The status column in this file compares this account against thresholds you control — start with the placeholders, then replace them with this client's own 90-day trailing range. That is the only benchmark that survives a client asking "compared to what?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Days in the period (calendar)</t>
-        </is>
-      </c>
-      <c r="B8" s="67">
-        <f>'KPI Calc'!$C$4-'KPI Calc'!$B$4+1</f>
-        <v/>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>Compare with the row above. A big gap means missing sync days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>First date in the data</t>
-        </is>
-      </c>
-      <c r="B9" s="92">
-        <f>IFERROR(MIN(Fundamentals!$A$2:$A$6000),0)</f>
-        <v/>
-      </c>
-      <c r="C9" s="37" t="inlineStr">
-        <is>
-          <t>Sanity-check the year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Last date in the data</t>
-        </is>
-      </c>
-      <c r="B10" s="92">
-        <f>IFERROR(MAX(Fundamentals!$A$2:$A$6000),0)</f>
-        <v/>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>Should be yesterday or today if the pipeline is healthy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>Meta rows in period</t>
-        </is>
-      </c>
-      <c r="B11" s="67">
-        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4,Fundamentals!$B$2:$B$6000,"Meta")</f>
-        <v/>
-      </c>
-      <c r="C11" s="37" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>TikTok rows in period</t>
-        </is>
-      </c>
-      <c r="B12" s="67">
-        <f>COUNTIFS(Fundamentals!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,Fundamentals!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4,Fundamentals!$B$2:$B$6000,"TikTok")</f>
-        <v/>
-      </c>
-      <c r="C12" s="37" t="inlineStr"/>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CHECKS  —  red means fix the DATA, not the campaign</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>Data exists for the selected period</t>
-        </is>
-      </c>
-      <c r="B17" s="93">
-        <f>IF('KPI Calc'!$B$10&gt;0,"OK","FIX")</f>
-        <v/>
-      </c>
-      <c r="C17" s="37" t="inlineStr">
-        <is>
-          <t>No impressions in the period means the date cells are wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Clicks never exceed impressions</t>
-        </is>
-      </c>
-      <c r="B18" s="93">
-        <f>IF('KPI Calc'!$B$12&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
-        <v/>
-      </c>
-      <c r="C18" s="37" t="inlineStr">
-        <is>
-          <t>A clicks &gt; impressions read almost always means the wrong click column was pulled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>Purchases never exceed clicks</t>
-        </is>
-      </c>
-      <c r="B19" s="93">
-        <f>IF('KPI Calc'!$B$16&gt;'KPI Calc'!$B$12,"FIX","OK")</f>
-        <v/>
-      </c>
-      <c r="C19" s="37" t="inlineStr">
-        <is>
-          <t>Either a view-through-heavy attribution window or mismatched date ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>Add to cart never exceeds clicks</t>
-        </is>
-      </c>
-      <c r="B20" s="93">
-        <f>IF('KPI Calc'!$B$14&gt;'KPI Calc'!$B$12,"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C20" s="37" t="inlineStr">
-        <is>
-          <t>Cross-platform ATC can exceed clicks if windows differ between platforms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>Reach never exceeds impressions</t>
-        </is>
-      </c>
-      <c r="B21" s="93">
-        <f>IF('KPI Calc'!$B$11&gt;'KPI Calc'!$B$10,"FIX","OK")</f>
-        <v/>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>Reach is deduplicated, so this is a hard rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>Revenue is present</t>
-        </is>
-      </c>
-      <c r="B22" s="93">
-        <f>IF('KPI Calc'!$B$17&lt;=0,"FIX","OK")</f>
-        <v/>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>Without purchase value there is no ROAS, no AOV and no story to tell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Ad spend reconciles to ad-level spend</t>
-        </is>
-      </c>
-      <c r="B23" s="93">
-        <f>IF(ABS(SUMIFS('Ad Data'!$G$2:$G$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$9)/MAX(1,'KPI Calc'!$B$9)&gt;0.05,"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C23" s="37" t="inlineStr">
-        <is>
-          <t>Sums ad-level spend for the SAME dates as the period, then compares it with account-level spend. More than 5% apart means the ad-level export is incomplete.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>Ad-level purchases reconcile</t>
-        </is>
-      </c>
-      <c r="B24" s="93">
-        <f>IF(ABS(SUMIFS('Ad Data'!$J$2:$J$6000,'Ad Data'!$A$2:$A$6000,"&gt;="&amp;'KPI Calc'!$B$4,'Ad Data'!$A$2:$A$6000,"&lt;="&amp;'KPI Calc'!$C$4)-'KPI Calc'!$B$16)/MAX(1,'KPI Calc'!$B$16)&gt;0.08,"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C24" s="37" t="inlineStr">
-        <is>
-          <t>Ad-level and account-level purchase counts should be close over the same dates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>Checkout does not exceed add to cart</t>
-        </is>
-      </c>
-      <c r="B25" s="93">
-        <f>IF('KPI Calc'!$B$15&gt;'KPI Calc'!$B$14,"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C25" s="37" t="inlineStr">
-        <is>
-          <t>Initiate-checkout above add-to-cart breaks the funnel ladder. Usually a buy-now button that skips the cart, or events that are counted on the wrong step — confirm which before you quote the funnel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>Business inputs are filled in</t>
-        </is>
-      </c>
-      <c r="B26" s="93">
-        <f>IF(OR('KPI Calc'!$J$5&lt;=0,'KPI Calc'!$J$7&lt;=0),"FIX","OK")</f>
-        <v/>
-      </c>
-      <c r="C26" s="37" t="inlineStr">
-        <is>
-          <t>COGS % and shipping per order drive every profit number in the kit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>Contribution margin is plausible</t>
-        </is>
-      </c>
-      <c r="B27" s="93">
-        <f>IF(OR('KPI Calc'!$B$33&lt;=0,'KPI Calc'!$B$33&gt;=1),"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C27" s="37" t="inlineStr">
-        <is>
-          <t>A margin outside 0–100% means a cost input is wrong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>No blank platforms in Fundamentals</t>
-        </is>
-      </c>
-      <c r="B28" s="93">
-        <f>IF(SUMPRODUCT((Fundamentals!$A$2:$A$6000&lt;&gt;"")*(Fundamentals!$B$2:$B$6000=""))&gt;0,"CHECK","OK")</f>
-        <v/>
-      </c>
-      <c r="C28" s="37" t="inlineStr">
-        <is>
-          <t>Counts only rows that carry a date -- the empty rows below your data are normal and are ignored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>Benchmarks retuned for this account</t>
-        </is>
-      </c>
-      <c r="B29" s="93">
-        <f>IF(Benchmarks!$B$28="TUNED","OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="C29" s="37" t="inlineStr">
-        <is>
-          <t>The Benchmarks tab still holds the shipped placeholders. Replace them with this client's own range, then set Benchmarks!B28 to TUNED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="94">
-        <f>IF(COUNTIF(B17:B29,"FIX")&gt;0,"⛔ "&amp;COUNTIF(B17:B29,"FIX")&amp;" check(s) need fixing before you report these numbers.",IF(COUNTIF(B17:B29,"CHECK")&gt;0,"⚠ "&amp;COUNTIF(B17:B29,"CHECK")&amp;" thing(s) to verify. They are usually benign — but verify them.","✅ All "&amp;COUNTA(B17:B29)&amp;" checks passed. This data is safe to report."))</f>
-        <v/>
-      </c>
-      <c r="B31" s="58" t="n"/>
-      <c r="C31" s="58" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="E7:F20"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A15:C15"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B17:B29">
-    <cfRule type="expression" priority="1" dxfId="6">
-      <formula>B17="FIX"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="7">
-      <formula>B17="CHECK"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="8">
-      <formula>B17="OK"</formula>
+    <cfRule type="expression" priority="6" dxfId="8">
+      <formula>AND($K6&lt;&gt;"",$K6&lt;'KPI Calc'!$B$35)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
